--- a/research/traditional_assets/database/data/south_korea/south_korea_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_real_estate_general_diversified.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="kose_a034830" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,10 +590,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0591</v>
+        <v>-0.0747</v>
       </c>
       <c r="E2">
-        <v>0.111</v>
+        <v>-0.192</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,94 +608,97 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>106.4</v>
+        <v>46.1</v>
       </c>
       <c r="L2">
-        <v>0.6164542294322133</v>
+        <v>0.4324577861163227</v>
       </c>
       <c r="M2">
-        <v>18.518</v>
+        <v>15.96</v>
       </c>
       <c r="N2">
-        <v>0.03711022044088177</v>
+        <v>0.06754126110876005</v>
       </c>
       <c r="O2">
-        <v>0.1740413533834586</v>
+        <v>0.3462039045553145</v>
       </c>
       <c r="P2">
-        <v>17.328</v>
+        <v>15.96</v>
       </c>
       <c r="Q2">
-        <v>0.03472545090180361</v>
+        <v>0.06754126110876005</v>
       </c>
       <c r="R2">
-        <v>0.1628571428571428</v>
+        <v>0.3462039045553145</v>
       </c>
       <c r="S2">
-        <v>1.190000000000001</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.06426179933038131</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>211</v>
+        <v>156.6</v>
       </c>
       <c r="V2">
-        <v>0.4228456913827655</v>
+        <v>0.6627168853152772</v>
       </c>
       <c r="W2">
-        <v>0.1373434878017297</v>
+        <v>0.05497912939773405</v>
       </c>
       <c r="X2">
-        <v>0.05940088875865298</v>
+        <v>0.1147026282978282</v>
       </c>
       <c r="Y2">
-        <v>0.07794259904307671</v>
+        <v>-0.0597234989000941</v>
       </c>
       <c r="Z2">
-        <v>0.1761062759542491</v>
+        <v>0.1037742277776155</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04211107010645439</v>
+        <v>0.0703123931190876</v>
       </c>
       <c r="AC2">
-        <v>-0.04211107010645439</v>
+        <v>-0.0703123931190876</v>
       </c>
       <c r="AD2">
-        <v>402.5</v>
+        <v>346.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>402.5</v>
+        <v>346.1</v>
       </c>
       <c r="AG2">
-        <v>191.5</v>
+        <v>189.5</v>
       </c>
       <c r="AH2">
-        <v>0.4464780920687743</v>
+        <v>0.5942651098901098</v>
       </c>
       <c r="AI2">
-        <v>0.3235270476649788</v>
+        <v>0.3250986285928988</v>
       </c>
       <c r="AJ2">
-        <v>0.277335264301231</v>
+        <v>0.4450446218882104</v>
       </c>
       <c r="AK2">
-        <v>0.1853644371309651</v>
+        <v>0.2087004405286344</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="AM2">
-        <v>-0.337</v>
+        <v>0.131</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0591</v>
+        <v>-0.0747</v>
       </c>
       <c r="E3">
-        <v>0.111</v>
+        <v>-0.192</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,94 +736,8798 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>106.4</v>
+        <v>46.1</v>
       </c>
       <c r="L3">
-        <v>0.6164542294322133</v>
+        <v>0.4324577861163227</v>
       </c>
       <c r="M3">
-        <v>18.518</v>
+        <v>15.96</v>
       </c>
       <c r="N3">
-        <v>0.03711022044088177</v>
+        <v>0.06754126110876005</v>
       </c>
       <c r="O3">
-        <v>0.1740413533834586</v>
+        <v>0.3462039045553145</v>
       </c>
       <c r="P3">
-        <v>17.328</v>
+        <v>15.96</v>
       </c>
       <c r="Q3">
-        <v>0.03472545090180361</v>
+        <v>0.06754126110876005</v>
       </c>
       <c r="R3">
-        <v>0.1628571428571428</v>
+        <v>0.3462039045553145</v>
       </c>
       <c r="S3">
-        <v>1.190000000000001</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.06426179933038131</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>211</v>
+        <v>156.6</v>
       </c>
       <c r="V3">
-        <v>0.4228456913827655</v>
+        <v>0.6627168853152772</v>
       </c>
       <c r="W3">
-        <v>0.1373434878017297</v>
+        <v>0.05497912939773405</v>
       </c>
       <c r="X3">
-        <v>0.05940088875865298</v>
+        <v>0.1147026282978282</v>
       </c>
       <c r="Y3">
-        <v>0.07794259904307671</v>
+        <v>-0.0597234989000941</v>
       </c>
       <c r="Z3">
-        <v>0.1761062759542491</v>
+        <v>0.1037742277776155</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04211107010645439</v>
+        <v>0.0703123931190876</v>
       </c>
       <c r="AC3">
-        <v>-0.04211107010645439</v>
+        <v>-0.0703123931190876</v>
       </c>
       <c r="AD3">
-        <v>402.5</v>
+        <v>346.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>402.5</v>
+        <v>346.1</v>
       </c>
       <c r="AG3">
-        <v>191.5</v>
+        <v>189.5</v>
       </c>
       <c r="AH3">
-        <v>0.4464780920687743</v>
+        <v>0.5942651098901098</v>
       </c>
       <c r="AI3">
-        <v>0.3235270476649788</v>
+        <v>0.3250986285928988</v>
       </c>
       <c r="AJ3">
-        <v>0.277335264301231</v>
+        <v>0.4450446218882104</v>
       </c>
       <c r="AK3">
-        <v>0.1853644371309651</v>
+        <v>0.2087004405286344</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="AM3">
-        <v>-0.337</v>
+        <v>0.131</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KOREIT (KOSE:A034830)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KOSE:A034830</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Real Estate (General/Diversified)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.5942651098901101</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>236.3</v>
+      </c>
+      <c r="H2">
+        <v>472.404355685131</v>
+      </c>
+      <c r="I2">
+        <v>425.8</v>
+      </c>
+      <c r="J2">
+        <v>321.628355685131</v>
+      </c>
+      <c r="K2">
+        <v>346.1</v>
+      </c>
+      <c r="L2">
+        <v>5.824</v>
+      </c>
+      <c r="M2">
+        <v>0.0703123931190876</v>
+      </c>
+      <c r="N2">
+        <v>0.08051888688584249</v>
+      </c>
+      <c r="O2">
+        <v>0.0400049311926606</v>
+      </c>
+      <c r="P2">
+        <v>0.547007417582418</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.114702628297828</v>
+      </c>
+      <c r="T2">
+        <v>0.0758068815252711</v>
+      </c>
+      <c r="U2">
+        <v>1.12178368472357</v>
+      </c>
+      <c r="V2">
+        <v>0.546933839427207</v>
+      </c>
+      <c r="W2">
+        <v>-5.162603309588232</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>236.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.06766244627325971</v>
+      </c>
+      <c r="AC2">
+        <v>0.05333990825688074</v>
+      </c>
+      <c r="AD2">
+        <v>0.25</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>7.18</v>
+      </c>
+      <c r="AI2">
+        <v>1.028</v>
+      </c>
+      <c r="AJ2">
+        <v>346.1</v>
+      </c>
+      <c r="AK2">
+        <v>346.1</v>
+      </c>
+      <c r="AL2">
+        <v>0.157</v>
+      </c>
+      <c r="AM2">
+        <v>346.1</v>
+      </c>
+      <c r="AN2">
+        <v>156.6</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-346.1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>156.6</v>
+      </c>
+      <c r="H2">
+        <v>236.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>7.18</v>
+      </c>
+      <c r="L2">
+        <v>-7.18</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-7.18</v>
+      </c>
+      <c r="O2">
+        <v>-1.795</v>
+      </c>
+      <c r="P2">
+        <v>-5.385</v>
+      </c>
+      <c r="Q2">
+        <v>1.795</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08051888688584254</v>
+      </c>
+      <c r="C3">
+        <v>472.4043556851308</v>
+      </c>
+      <c r="D3">
+        <v>321.6283556851308</v>
+      </c>
+      <c r="E3">
+        <v>-340.276</v>
+      </c>
+      <c r="F3">
+        <v>5.824000000000001</v>
+      </c>
+      <c r="G3">
+        <v>156.6</v>
+      </c>
+      <c r="H3">
+        <v>236.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>7.18</v>
+      </c>
+      <c r="L3">
+        <v>-7.18</v>
+      </c>
+      <c r="M3">
+        <v>1.3907712</v>
+      </c>
+      <c r="N3">
+        <v>-8.570771199999999</v>
+      </c>
+      <c r="O3">
+        <v>-2.1426928</v>
+      </c>
+      <c r="P3">
+        <v>-6.4280784</v>
+      </c>
+      <c r="Q3">
+        <v>0.7519216000000002</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.07580688152527107</v>
+      </c>
+      <c r="T3">
+        <v>0.5469338394272073</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-1.290650827397058</v>
+      </c>
+      <c r="W3">
+        <v>0.5470074175824176</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-5.162603309588232</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08251888688584252</v>
+      </c>
+      <c r="C4">
+        <v>451.8668815509445</v>
+      </c>
+      <c r="D4">
+        <v>306.9148815509446</v>
+      </c>
+      <c r="E4">
+        <v>-334.452</v>
+      </c>
+      <c r="F4">
+        <v>11.648</v>
+      </c>
+      <c r="G4">
+        <v>156.6</v>
+      </c>
+      <c r="H4">
+        <v>236.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>7.18</v>
+      </c>
+      <c r="L4">
+        <v>-7.18</v>
+      </c>
+      <c r="M4">
+        <v>2.781542400000001</v>
+      </c>
+      <c r="N4">
+        <v>-9.961542400000001</v>
+      </c>
+      <c r="O4">
+        <v>-2.4903856</v>
+      </c>
+      <c r="P4">
+        <v>-7.471156800000001</v>
+      </c>
+      <c r="Q4">
+        <v>-0.2911568000000013</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.07618450276532485</v>
+      </c>
+      <c r="T4">
+        <v>0.5525147969723829</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-0.6453254136985291</v>
+      </c>
+      <c r="W4">
+        <v>0.3929037087912088</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-2.581301654794117</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08451888688584253</v>
+      </c>
+      <c r="C5">
+        <v>432.6167068360048</v>
+      </c>
+      <c r="D5">
+        <v>293.4887068360048</v>
+      </c>
+      <c r="E5">
+        <v>-328.628</v>
+      </c>
+      <c r="F5">
+        <v>17.472</v>
+      </c>
+      <c r="G5">
+        <v>156.6</v>
+      </c>
+      <c r="H5">
+        <v>236.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>7.18</v>
+      </c>
+      <c r="L5">
+        <v>-7.18</v>
+      </c>
+      <c r="M5">
+        <v>4.172313600000001</v>
+      </c>
+      <c r="N5">
+        <v>-11.3523136</v>
+      </c>
+      <c r="O5">
+        <v>-2.8380784</v>
+      </c>
+      <c r="P5">
+        <v>-8.5142352</v>
+      </c>
+      <c r="Q5">
+        <v>-1.3342352</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.0765699100103282</v>
+      </c>
+      <c r="T5">
+        <v>0.5582108258071498</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-0.4302169424656861</v>
+      </c>
+      <c r="W5">
+        <v>0.3415358058608058</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-1.720867769862744</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08651888688584253</v>
+      </c>
+      <c r="C6">
+        <v>414.491971173913</v>
+      </c>
+      <c r="D6">
+        <v>281.187971173913</v>
+      </c>
+      <c r="E6">
+        <v>-322.804</v>
+      </c>
+      <c r="F6">
+        <v>23.296</v>
+      </c>
+      <c r="G6">
+        <v>156.6</v>
+      </c>
+      <c r="H6">
+        <v>236.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>7.18</v>
+      </c>
+      <c r="L6">
+        <v>-7.18</v>
+      </c>
+      <c r="M6">
+        <v>5.563084800000001</v>
+      </c>
+      <c r="N6">
+        <v>-12.7430848</v>
+      </c>
+      <c r="O6">
+        <v>-3.1857712</v>
+      </c>
+      <c r="P6">
+        <v>-9.557313600000001</v>
+      </c>
+      <c r="Q6">
+        <v>-2.377313600000001</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.0769633465729358</v>
+      </c>
+      <c r="T6">
+        <v>0.5640255219093075</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-0.3226627068492646</v>
+      </c>
+      <c r="W6">
+        <v>0.3158518543956044</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-1.290650827397058</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08851888688584253</v>
+      </c>
+      <c r="C7">
+        <v>397.3568582835727</v>
+      </c>
+      <c r="D7">
+        <v>269.8768582835727</v>
+      </c>
+      <c r="E7">
+        <v>-316.98</v>
+      </c>
+      <c r="F7">
+        <v>29.12</v>
+      </c>
+      <c r="G7">
+        <v>156.6</v>
+      </c>
+      <c r="H7">
+        <v>236.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>7.18</v>
+      </c>
+      <c r="L7">
+        <v>-7.18</v>
+      </c>
+      <c r="M7">
+        <v>6.953856000000002</v>
+      </c>
+      <c r="N7">
+        <v>-14.133856</v>
+      </c>
+      <c r="O7">
+        <v>-3.533464</v>
+      </c>
+      <c r="P7">
+        <v>-10.600392</v>
+      </c>
+      <c r="Q7">
+        <v>-3.420392000000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.07736506601054563</v>
+      </c>
+      <c r="T7">
+        <v>0.5699626326662476</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-0.2581301654794116</v>
+      </c>
+      <c r="W7">
+        <v>0.3004414835164835</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-1.032520661917646</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09051888688584252</v>
+      </c>
+      <c r="C8">
+        <v>381.0965602681392</v>
+      </c>
+      <c r="D8">
+        <v>259.4405602681392</v>
+      </c>
+      <c r="E8">
+        <v>-311.156</v>
+      </c>
+      <c r="F8">
+        <v>34.944</v>
+      </c>
+      <c r="G8">
+        <v>156.6</v>
+      </c>
+      <c r="H8">
+        <v>236.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>7.18</v>
+      </c>
+      <c r="L8">
+        <v>-7.18</v>
+      </c>
+      <c r="M8">
+        <v>8.344627200000001</v>
+      </c>
+      <c r="N8">
+        <v>-15.5246272</v>
+      </c>
+      <c r="O8">
+        <v>-3.8811568</v>
+      </c>
+      <c r="P8">
+        <v>-11.6434704</v>
+      </c>
+      <c r="Q8">
+        <v>-4.463470400000002</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.07777533267023229</v>
+      </c>
+      <c r="T8">
+        <v>0.5760260649286545</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-0.215108471232843</v>
+      </c>
+      <c r="W8">
+        <v>0.290167902930403</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-0.8604338849313722</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09251888688584253</v>
+      </c>
+      <c r="C9">
+        <v>365.6133668146533</v>
+      </c>
+      <c r="D9">
+        <v>249.7813668146533</v>
+      </c>
+      <c r="E9">
+        <v>-305.332</v>
+      </c>
+      <c r="F9">
+        <v>40.76800000000001</v>
+      </c>
+      <c r="G9">
+        <v>156.6</v>
+      </c>
+      <c r="H9">
+        <v>236.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>7.18</v>
+      </c>
+      <c r="L9">
+        <v>-7.18</v>
+      </c>
+      <c r="M9">
+        <v>9.735398400000003</v>
+      </c>
+      <c r="N9">
+        <v>-16.9153984</v>
+      </c>
+      <c r="O9">
+        <v>-4.2288496</v>
+      </c>
+      <c r="P9">
+        <v>-12.6865488</v>
+      </c>
+      <c r="Q9">
+        <v>-5.506548800000001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.07819442226883694</v>
+      </c>
+      <c r="T9">
+        <v>0.5822198935838013</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-0.1843786896281512</v>
+      </c>
+      <c r="W9">
+        <v>0.2828296310832025</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-0.7375147585126045</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09451888688584255</v>
+      </c>
+      <c r="C10">
+        <v>350.8235966503494</v>
+      </c>
+      <c r="D10">
+        <v>240.8155966503494</v>
+      </c>
+      <c r="E10">
+        <v>-299.508</v>
+      </c>
+      <c r="F10">
+        <v>46.59200000000001</v>
+      </c>
+      <c r="G10">
+        <v>156.6</v>
+      </c>
+      <c r="H10">
+        <v>236.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>7.18</v>
+      </c>
+      <c r="L10">
+        <v>-7.18</v>
+      </c>
+      <c r="M10">
+        <v>11.1261696</v>
+      </c>
+      <c r="N10">
+        <v>-18.3061696</v>
+      </c>
+      <c r="O10">
+        <v>-4.576542400000001</v>
+      </c>
+      <c r="P10">
+        <v>-13.7296272</v>
+      </c>
+      <c r="Q10">
+        <v>-6.549627200000003</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.07862262251088953</v>
+      </c>
+      <c r="T10">
+        <v>0.5885483706879732</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-0.1613313534246323</v>
+      </c>
+      <c r="W10">
+        <v>0.2773259271978022</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-0.6453254136985294</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09651888688584254</v>
+      </c>
+      <c r="C11">
+        <v>336.6551669621388</v>
+      </c>
+      <c r="D11">
+        <v>232.4711669621388</v>
+      </c>
+      <c r="E11">
+        <v>-293.684</v>
+      </c>
+      <c r="F11">
+        <v>52.416</v>
+      </c>
+      <c r="G11">
+        <v>156.6</v>
+      </c>
+      <c r="H11">
+        <v>236.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>7.18</v>
+      </c>
+      <c r="L11">
+        <v>-7.18</v>
+      </c>
+      <c r="M11">
+        <v>12.5169408</v>
+      </c>
+      <c r="N11">
+        <v>-19.6969408</v>
+      </c>
+      <c r="O11">
+        <v>-4.9242352</v>
+      </c>
+      <c r="P11">
+        <v>-14.7727056</v>
+      </c>
+      <c r="Q11">
+        <v>-7.5927056</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.07906023374727292</v>
+      </c>
+      <c r="T11">
+        <v>0.5950159352010278</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-0.143405647488562</v>
+      </c>
+      <c r="W11">
+        <v>0.2730452686202686</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-0.573622589954248</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09851888688584254</v>
+      </c>
+      <c r="C12">
+        <v>323.0456512204764</v>
+      </c>
+      <c r="D12">
+        <v>224.6856512204764</v>
+      </c>
+      <c r="E12">
+        <v>-287.86</v>
+      </c>
+      <c r="F12">
+        <v>58.24000000000001</v>
+      </c>
+      <c r="G12">
+        <v>156.6</v>
+      </c>
+      <c r="H12">
+        <v>236.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>7.18</v>
+      </c>
+      <c r="L12">
+        <v>-7.18</v>
+      </c>
+      <c r="M12">
+        <v>13.907712</v>
+      </c>
+      <c r="N12">
+        <v>-21.087712</v>
+      </c>
+      <c r="O12">
+        <v>-5.271928000000001</v>
+      </c>
+      <c r="P12">
+        <v>-15.815784</v>
+      </c>
+      <c r="Q12">
+        <v>-8.635784000000003</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.07950756967779818</v>
+      </c>
+      <c r="T12">
+        <v>0.601627223369928</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.1290650827397058</v>
+      </c>
+      <c r="W12">
+        <v>0.2696207417582417</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-0.5162603309588232</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1005188868858425</v>
+      </c>
+      <c r="C13">
+        <v>309.9407146204349</v>
+      </c>
+      <c r="D13">
+        <v>217.404714620435</v>
+      </c>
+      <c r="E13">
+        <v>-282.036</v>
+      </c>
+      <c r="F13">
+        <v>64.06400000000001</v>
+      </c>
+      <c r="G13">
+        <v>156.6</v>
+      </c>
+      <c r="H13">
+        <v>236.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>7.18</v>
+      </c>
+      <c r="L13">
+        <v>-7.18</v>
+      </c>
+      <c r="M13">
+        <v>15.2984832</v>
+      </c>
+      <c r="N13">
+        <v>-22.4784832</v>
+      </c>
+      <c r="O13">
+        <v>-5.619620800000001</v>
+      </c>
+      <c r="P13">
+        <v>-16.8588624</v>
+      </c>
+      <c r="Q13">
+        <v>-9.678862400000003</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.07996495810114422</v>
+      </c>
+      <c r="T13">
+        <v>0.6083870798122868</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.1173318933997326</v>
+      </c>
+      <c r="W13">
+        <v>0.2668188561438561</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-0.4693275735989302</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1025188868858425</v>
+      </c>
+      <c r="C14">
+        <v>297.2928441717897</v>
+      </c>
+      <c r="D14">
+        <v>210.5808441717897</v>
+      </c>
+      <c r="E14">
+        <v>-276.212</v>
+      </c>
+      <c r="F14">
+        <v>69.88800000000001</v>
+      </c>
+      <c r="G14">
+        <v>156.6</v>
+      </c>
+      <c r="H14">
+        <v>236.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>7.18</v>
+      </c>
+      <c r="L14">
+        <v>-7.18</v>
+      </c>
+      <c r="M14">
+        <v>16.6892544</v>
+      </c>
+      <c r="N14">
+        <v>-23.8692544</v>
+      </c>
+      <c r="O14">
+        <v>-5.967313600000001</v>
+      </c>
+      <c r="P14">
+        <v>-17.9019408</v>
+      </c>
+      <c r="Q14">
+        <v>-10.7219408</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08043274171592996</v>
+      </c>
+      <c r="T14">
+        <v>0.6153005693556082</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.1075542356164215</v>
+      </c>
+      <c r="W14">
+        <v>0.2644839514652014</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-0.4302169424656861</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1045188868858425</v>
+      </c>
+      <c r="C15">
+        <v>285.0603106694624</v>
+      </c>
+      <c r="D15">
+        <v>204.1723106694624</v>
+      </c>
+      <c r="E15">
+        <v>-270.388</v>
+      </c>
+      <c r="F15">
+        <v>75.71200000000002</v>
+      </c>
+      <c r="G15">
+        <v>156.6</v>
+      </c>
+      <c r="H15">
+        <v>236.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>7.18</v>
+      </c>
+      <c r="L15">
+        <v>-7.18</v>
+      </c>
+      <c r="M15">
+        <v>18.08002560000001</v>
+      </c>
+      <c r="N15">
+        <v>-25.26002560000001</v>
+      </c>
+      <c r="O15">
+        <v>-6.315006400000001</v>
+      </c>
+      <c r="P15">
+        <v>-18.9450192</v>
+      </c>
+      <c r="Q15">
+        <v>-11.7650192</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.0809112789770326</v>
+      </c>
+      <c r="T15">
+        <v>0.6223729896930291</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.09928083287669677</v>
+      </c>
+      <c r="W15">
+        <v>0.2625082628909552</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-0.397123331506787</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1065188868858425</v>
+      </c>
+      <c r="C16">
+        <v>273.2063146060703</v>
+      </c>
+      <c r="D16">
+        <v>198.1423146060703</v>
+      </c>
+      <c r="E16">
+        <v>-264.564</v>
+      </c>
+      <c r="F16">
+        <v>81.53600000000002</v>
+      </c>
+      <c r="G16">
+        <v>156.6</v>
+      </c>
+      <c r="H16">
+        <v>236.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>7.18</v>
+      </c>
+      <c r="L16">
+        <v>-7.18</v>
+      </c>
+      <c r="M16">
+        <v>19.47079680000001</v>
+      </c>
+      <c r="N16">
+        <v>-26.65079680000001</v>
+      </c>
+      <c r="O16">
+        <v>-6.662699200000001</v>
+      </c>
+      <c r="P16">
+        <v>-19.9880976</v>
+      </c>
+      <c r="Q16">
+        <v>-12.8080976</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08140094501164925</v>
+      </c>
+      <c r="T16">
+        <v>0.6296098849220177</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.09218934481407558</v>
+      </c>
+      <c r="W16">
+        <v>0.2608148155416012</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-0.3687573792563024</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1085188868858425</v>
+      </c>
+      <c r="C17">
+        <v>261.6982790898261</v>
+      </c>
+      <c r="D17">
+        <v>192.4582790898261</v>
+      </c>
+      <c r="E17">
+        <v>-258.74</v>
+      </c>
+      <c r="F17">
+        <v>87.36000000000001</v>
+      </c>
+      <c r="G17">
+        <v>156.6</v>
+      </c>
+      <c r="H17">
+        <v>236.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>7.18</v>
+      </c>
+      <c r="L17">
+        <v>-7.18</v>
+      </c>
+      <c r="M17">
+        <v>20.86156800000001</v>
+      </c>
+      <c r="N17">
+        <v>-28.04156800000001</v>
+      </c>
+      <c r="O17">
+        <v>-7.010392000000001</v>
+      </c>
+      <c r="P17">
+        <v>-21.031176</v>
+      </c>
+      <c r="Q17">
+        <v>-13.851176</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.0819021326000216</v>
+      </c>
+      <c r="T17">
+        <v>0.6370170600387475</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.08604338849313721</v>
+      </c>
+      <c r="W17">
+        <v>0.2593471611721612</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-0.3441735539725488</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1105188868858425</v>
+      </c>
+      <c r="C18">
+        <v>250.5072610713739</v>
+      </c>
+      <c r="D18">
+        <v>187.0912610713739</v>
+      </c>
+      <c r="E18">
+        <v>-252.916</v>
+      </c>
+      <c r="F18">
+        <v>93.18400000000001</v>
+      </c>
+      <c r="G18">
+        <v>156.6</v>
+      </c>
+      <c r="H18">
+        <v>236.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>7.18</v>
+      </c>
+      <c r="L18">
+        <v>-7.18</v>
+      </c>
+      <c r="M18">
+        <v>22.25233920000001</v>
+      </c>
+      <c r="N18">
+        <v>-29.4323392</v>
+      </c>
+      <c r="O18">
+        <v>-7.358084800000001</v>
+      </c>
+      <c r="P18">
+        <v>-22.0742544</v>
+      </c>
+      <c r="Q18">
+        <v>-14.8942544</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08241525322621233</v>
+      </c>
+      <c r="T18">
+        <v>0.6446005964677801</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.08066567671231614</v>
+      </c>
+      <c r="W18">
+        <v>0.2580629635989011</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-0.3226627068492645</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1125188868858426</v>
+      </c>
+      <c r="C19">
+        <v>239.6074584114369</v>
+      </c>
+      <c r="D19">
+        <v>182.015458411437</v>
+      </c>
+      <c r="E19">
+        <v>-247.092</v>
+      </c>
+      <c r="F19">
+        <v>99.00800000000002</v>
+      </c>
+      <c r="G19">
+        <v>156.6</v>
+      </c>
+      <c r="H19">
+        <v>236.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>7.18</v>
+      </c>
+      <c r="L19">
+        <v>-7.18</v>
+      </c>
+      <c r="M19">
+        <v>23.64311040000001</v>
+      </c>
+      <c r="N19">
+        <v>-30.82311040000001</v>
+      </c>
+      <c r="O19">
+        <v>-7.705777600000002</v>
+      </c>
+      <c r="P19">
+        <v>-23.11733280000001</v>
+      </c>
+      <c r="Q19">
+        <v>-15.93733280000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08294073820484141</v>
+      </c>
+      <c r="T19">
+        <v>0.6523668687143799</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.0759206369057093</v>
+      </c>
+      <c r="W19">
+        <v>0.2569298480930834</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-0.3036825476228371</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1145188868858425</v>
+      </c>
+      <c r="C20">
+        <v>228.9757950688459</v>
+      </c>
+      <c r="D20">
+        <v>177.2077950688459</v>
+      </c>
+      <c r="E20">
+        <v>-241.268</v>
+      </c>
+      <c r="F20">
+        <v>104.832</v>
+      </c>
+      <c r="G20">
+        <v>156.6</v>
+      </c>
+      <c r="H20">
+        <v>236.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>7.18</v>
+      </c>
+      <c r="L20">
+        <v>-7.18</v>
+      </c>
+      <c r="M20">
+        <v>25.0338816</v>
+      </c>
+      <c r="N20">
+        <v>-32.21388160000001</v>
+      </c>
+      <c r="O20">
+        <v>-8.053470400000002</v>
+      </c>
+      <c r="P20">
+        <v>-24.16041120000001</v>
+      </c>
+      <c r="Q20">
+        <v>-16.98041120000001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08347903989026628</v>
+      </c>
+      <c r="T20">
+        <v>0.6603225622352868</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.07170282374428101</v>
+      </c>
+      <c r="W20">
+        <v>0.2559226343101343</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-0.2868112949771242</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1165188868858425</v>
+      </c>
+      <c r="C21">
+        <v>218.5915703366224</v>
+      </c>
+      <c r="D21">
+        <v>172.6475703366224</v>
+      </c>
+      <c r="E21">
+        <v>-235.444</v>
+      </c>
+      <c r="F21">
+        <v>110.656</v>
+      </c>
+      <c r="G21">
+        <v>156.6</v>
+      </c>
+      <c r="H21">
+        <v>236.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>7.18</v>
+      </c>
+      <c r="L21">
+        <v>-7.18</v>
+      </c>
+      <c r="M21">
+        <v>26.42465280000001</v>
+      </c>
+      <c r="N21">
+        <v>-33.60465280000001</v>
+      </c>
+      <c r="O21">
+        <v>-8.401163200000003</v>
+      </c>
+      <c r="P21">
+        <v>-25.20348960000001</v>
+      </c>
+      <c r="Q21">
+        <v>-18.02348960000001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08403063297533131</v>
+      </c>
+      <c r="T21">
+        <v>0.6684746926332534</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.06792899091563463</v>
+      </c>
+      <c r="W21">
+        <v>0.2550214430306535</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.2717159636625386</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1185188868858425</v>
+      </c>
+      <c r="C22">
+        <v>208.4361608781875</v>
+      </c>
+      <c r="D22">
+        <v>168.3161608781875</v>
+      </c>
+      <c r="E22">
+        <v>-229.62</v>
+      </c>
+      <c r="F22">
+        <v>116.48</v>
+      </c>
+      <c r="G22">
+        <v>156.6</v>
+      </c>
+      <c r="H22">
+        <v>236.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>7.18</v>
+      </c>
+      <c r="L22">
+        <v>-7.18</v>
+      </c>
+      <c r="M22">
+        <v>27.81542400000001</v>
+      </c>
+      <c r="N22">
+        <v>-34.99542400000001</v>
+      </c>
+      <c r="O22">
+        <v>-8.748856000000002</v>
+      </c>
+      <c r="P22">
+        <v>-26.246568</v>
+      </c>
+      <c r="Q22">
+        <v>-19.066568</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08459601588752294</v>
+      </c>
+      <c r="T22">
+        <v>0.6768306262911691</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.06453254136985291</v>
+      </c>
+      <c r="W22">
+        <v>0.2542103708791209</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.2581301654794117</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1205188868858425</v>
+      </c>
+      <c r="C23">
+        <v>198.492766518024</v>
+      </c>
+      <c r="D23">
+        <v>164.196766518024</v>
+      </c>
+      <c r="E23">
+        <v>-223.796</v>
+      </c>
+      <c r="F23">
+        <v>122.304</v>
+      </c>
+      <c r="G23">
+        <v>156.6</v>
+      </c>
+      <c r="H23">
+        <v>236.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>7.18</v>
+      </c>
+      <c r="L23">
+        <v>-7.18</v>
+      </c>
+      <c r="M23">
+        <v>29.20619520000001</v>
+      </c>
+      <c r="N23">
+        <v>-36.3861952</v>
+      </c>
+      <c r="O23">
+        <v>-9.096548800000001</v>
+      </c>
+      <c r="P23">
+        <v>-27.2896464</v>
+      </c>
+      <c r="Q23">
+        <v>-20.1096464</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08517571229116247</v>
+      </c>
+      <c r="T23">
+        <v>0.6853981025733358</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.06145956320938372</v>
+      </c>
+      <c r="W23">
+        <v>0.2534765436944009</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.2458382528375347</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1225188868858425</v>
+      </c>
+      <c r="C24">
+        <v>188.7461924699022</v>
+      </c>
+      <c r="D24">
+        <v>160.2741924699022</v>
+      </c>
+      <c r="E24">
+        <v>-217.972</v>
+      </c>
+      <c r="F24">
+        <v>128.128</v>
+      </c>
+      <c r="G24">
+        <v>156.6</v>
+      </c>
+      <c r="H24">
+        <v>236.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>7.18</v>
+      </c>
+      <c r="L24">
+        <v>-7.18</v>
+      </c>
+      <c r="M24">
+        <v>30.59696640000001</v>
+      </c>
+      <c r="N24">
+        <v>-37.77696640000001</v>
+      </c>
+      <c r="O24">
+        <v>-9.444241600000002</v>
+      </c>
+      <c r="P24">
+        <v>-28.3327248</v>
+      </c>
+      <c r="Q24">
+        <v>-21.1527248</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.08577027270515174</v>
+      </c>
+      <c r="T24">
+        <v>0.6941852577345323</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.05866594669986628</v>
+      </c>
+      <c r="W24">
+        <v>0.2528094280719281</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.2346637867994652</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1245188868858425</v>
+      </c>
+      <c r="C25">
+        <v>179.1826620515161</v>
+      </c>
+      <c r="D25">
+        <v>156.5346620515162</v>
+      </c>
+      <c r="E25">
+        <v>-212.148</v>
+      </c>
+      <c r="F25">
+        <v>133.952</v>
+      </c>
+      <c r="G25">
+        <v>156.6</v>
+      </c>
+      <c r="H25">
+        <v>236.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>7.18</v>
+      </c>
+      <c r="L25">
+        <v>-7.18</v>
+      </c>
+      <c r="M25">
+        <v>31.98773760000001</v>
+      </c>
+      <c r="N25">
+        <v>-39.16773760000001</v>
+      </c>
+      <c r="O25">
+        <v>-9.791934400000002</v>
+      </c>
+      <c r="P25">
+        <v>-29.37580320000001</v>
+      </c>
+      <c r="Q25">
+        <v>-22.19580320000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.08638027624677708</v>
+      </c>
+      <c r="T25">
+        <v>0.7032006506921237</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.05611525336508948</v>
+      </c>
+      <c r="W25">
+        <v>0.2522003225035834</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.224461013460358</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1265188868858425</v>
+      </c>
+      <c r="C26">
+        <v>169.7896550198781</v>
+      </c>
+      <c r="D26">
+        <v>152.9656550198781</v>
+      </c>
+      <c r="E26">
+        <v>-206.324</v>
+      </c>
+      <c r="F26">
+        <v>139.776</v>
+      </c>
+      <c r="G26">
+        <v>156.6</v>
+      </c>
+      <c r="H26">
+        <v>236.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>7.18</v>
+      </c>
+      <c r="L26">
+        <v>-7.18</v>
+      </c>
+      <c r="M26">
+        <v>33.37850880000001</v>
+      </c>
+      <c r="N26">
+        <v>-40.55850880000001</v>
+      </c>
+      <c r="O26">
+        <v>-10.1396272</v>
+      </c>
+      <c r="P26">
+        <v>-30.41888160000001</v>
+      </c>
+      <c r="Q26">
+        <v>-23.23888160000001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.08700633251318204</v>
+      </c>
+      <c r="T26">
+        <v>0.7124532908328095</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.05377711780821076</v>
+      </c>
+      <c r="W26">
+        <v>0.2516419757326007</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.215108471232843</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1285188868858425</v>
+      </c>
+      <c r="C27">
+        <v>160.5557675295327</v>
+      </c>
+      <c r="D27">
+        <v>149.5557675295327</v>
+      </c>
+      <c r="E27">
+        <v>-200.5</v>
+      </c>
+      <c r="F27">
+        <v>145.6</v>
+      </c>
+      <c r="G27">
+        <v>156.6</v>
+      </c>
+      <c r="H27">
+        <v>236.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>7.18</v>
+      </c>
+      <c r="L27">
+        <v>-7.18</v>
+      </c>
+      <c r="M27">
+        <v>34.76928000000001</v>
+      </c>
+      <c r="N27">
+        <v>-41.94928000000001</v>
+      </c>
+      <c r="O27">
+        <v>-10.48732</v>
+      </c>
+      <c r="P27">
+        <v>-31.46196</v>
+      </c>
+      <c r="Q27">
+        <v>-24.28196000000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.08764908361335781</v>
+      </c>
+      <c r="T27">
+        <v>0.7219526680439137</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.05162603309588232</v>
+      </c>
+      <c r="W27">
+        <v>0.2511282967032967</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.2065041323835293</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1305188868858425</v>
+      </c>
+      <c r="C28">
+        <v>151.4705904130751</v>
+      </c>
+      <c r="D28">
+        <v>146.2945904130751</v>
+      </c>
+      <c r="E28">
+        <v>-194.676</v>
+      </c>
+      <c r="F28">
+        <v>151.424</v>
+      </c>
+      <c r="G28">
+        <v>156.6</v>
+      </c>
+      <c r="H28">
+        <v>236.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>7.18</v>
+      </c>
+      <c r="L28">
+        <v>-7.18</v>
+      </c>
+      <c r="M28">
+        <v>36.16005120000001</v>
+      </c>
+      <c r="N28">
+        <v>-43.34005120000001</v>
+      </c>
+      <c r="O28">
+        <v>-10.8350128</v>
+      </c>
+      <c r="P28">
+        <v>-32.50503840000001</v>
+      </c>
+      <c r="Q28">
+        <v>-25.32503840000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.08830920636488968</v>
+      </c>
+      <c r="T28">
+        <v>0.7317087851796423</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.04964041643834839</v>
+      </c>
+      <c r="W28">
+        <v>0.2506541314454776</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.1985616657533935</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1325188868858426</v>
+      </c>
+      <c r="C29">
+        <v>142.5246030469367</v>
+      </c>
+      <c r="D29">
+        <v>143.1726030469367</v>
+      </c>
+      <c r="E29">
+        <v>-188.852</v>
+      </c>
+      <c r="F29">
+        <v>157.248</v>
+      </c>
+      <c r="G29">
+        <v>156.6</v>
+      </c>
+      <c r="H29">
+        <v>236.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>7.18</v>
+      </c>
+      <c r="L29">
+        <v>-7.18</v>
+      </c>
+      <c r="M29">
+        <v>37.55082240000002</v>
+      </c>
+      <c r="N29">
+        <v>-44.73082240000002</v>
+      </c>
+      <c r="O29">
+        <v>-11.1827056</v>
+      </c>
+      <c r="P29">
+        <v>-33.54811680000001</v>
+      </c>
+      <c r="Q29">
+        <v>-26.36811680000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.08898741467125804</v>
+      </c>
+      <c r="T29">
+        <v>0.7417321931958017</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.04780188249618733</v>
+      </c>
+      <c r="W29">
+        <v>0.2502150895400896</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.1912075299847493</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1345188868858425</v>
+      </c>
+      <c r="C30">
+        <v>133.7090805229089</v>
+      </c>
+      <c r="D30">
+        <v>140.1810805229089</v>
+      </c>
+      <c r="E30">
+        <v>-183.028</v>
+      </c>
+      <c r="F30">
+        <v>163.072</v>
+      </c>
+      <c r="G30">
+        <v>156.6</v>
+      </c>
+      <c r="H30">
+        <v>236.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>7.18</v>
+      </c>
+      <c r="L30">
+        <v>-7.18</v>
+      </c>
+      <c r="M30">
+        <v>38.94159360000001</v>
+      </c>
+      <c r="N30">
+        <v>-46.12159360000001</v>
+      </c>
+      <c r="O30">
+        <v>-11.5303984</v>
+      </c>
+      <c r="P30">
+        <v>-34.59119520000001</v>
+      </c>
+      <c r="Q30">
+        <v>-27.41119520000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.08968446209724773</v>
+      </c>
+      <c r="T30">
+        <v>0.7520340292124101</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.04609467240703779</v>
+      </c>
+      <c r="W30">
+        <v>0.2498074077708006</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.1843786896281512</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1365188868858425</v>
+      </c>
+      <c r="C31">
+        <v>125.0160122191189</v>
+      </c>
+      <c r="D31">
+        <v>137.3120122191189</v>
+      </c>
+      <c r="E31">
+        <v>-177.204</v>
+      </c>
+      <c r="F31">
+        <v>168.896</v>
+      </c>
+      <c r="G31">
+        <v>156.6</v>
+      </c>
+      <c r="H31">
+        <v>236.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>7.18</v>
+      </c>
+      <c r="L31">
+        <v>-7.18</v>
+      </c>
+      <c r="M31">
+        <v>40.33236480000001</v>
+      </c>
+      <c r="N31">
+        <v>-47.51236480000001</v>
+      </c>
+      <c r="O31">
+        <v>-11.8780912</v>
+      </c>
+      <c r="P31">
+        <v>-35.63427360000001</v>
+      </c>
+      <c r="Q31">
+        <v>-28.45427360000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09040114466199768</v>
+      </c>
+      <c r="T31">
+        <v>0.7626260577928665</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.04450520094472615</v>
+      </c>
+      <c r="W31">
+        <v>0.2494278419856006</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.1780208037789046</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1385188868858425</v>
+      </c>
+      <c r="C32">
+        <v>116.4380301700349</v>
+      </c>
+      <c r="D32">
+        <v>134.5580301700349</v>
+      </c>
+      <c r="E32">
+        <v>-171.38</v>
+      </c>
+      <c r="F32">
+        <v>174.72</v>
+      </c>
+      <c r="G32">
+        <v>156.6</v>
+      </c>
+      <c r="H32">
+        <v>236.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>7.18</v>
+      </c>
+      <c r="L32">
+        <v>-7.18</v>
+      </c>
+      <c r="M32">
+        <v>41.72313600000001</v>
+      </c>
+      <c r="N32">
+        <v>-48.90313600000001</v>
+      </c>
+      <c r="O32">
+        <v>-12.225784</v>
+      </c>
+      <c r="P32">
+        <v>-36.67735200000001</v>
+      </c>
+      <c r="Q32">
+        <v>-29.49735200000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.0911383038714548</v>
+      </c>
+      <c r="T32">
+        <v>0.7735207157613361</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.04302169424656861</v>
+      </c>
+      <c r="W32">
+        <v>0.2490735805860806</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.1720867769862744</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1405188868858425</v>
+      </c>
+      <c r="C33">
+        <v>107.9683458868192</v>
+      </c>
+      <c r="D33">
+        <v>131.9123458868193</v>
+      </c>
+      <c r="E33">
+        <v>-165.556</v>
+      </c>
+      <c r="F33">
+        <v>180.544</v>
+      </c>
+      <c r="G33">
+        <v>156.6</v>
+      </c>
+      <c r="H33">
+        <v>236.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>7.18</v>
+      </c>
+      <c r="L33">
+        <v>-7.18</v>
+      </c>
+      <c r="M33">
+        <v>43.11390720000001</v>
+      </c>
+      <c r="N33">
+        <v>-50.29390720000001</v>
+      </c>
+      <c r="O33">
+        <v>-12.5734768</v>
+      </c>
+      <c r="P33">
+        <v>-37.72043040000001</v>
+      </c>
+      <c r="Q33">
+        <v>-30.54043040000001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09189683001451936</v>
+      </c>
+      <c r="T33">
+        <v>0.7847311609172974</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.04163389765796961</v>
+      </c>
+      <c r="W33">
+        <v>0.2487421747607231</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.1665355906318784</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1425188868858425</v>
+      </c>
+      <c r="C34">
+        <v>99.60069448739753</v>
+      </c>
+      <c r="D34">
+        <v>129.3686944873975</v>
+      </c>
+      <c r="E34">
+        <v>-159.732</v>
+      </c>
+      <c r="F34">
+        <v>186.368</v>
+      </c>
+      <c r="G34">
+        <v>156.6</v>
+      </c>
+      <c r="H34">
+        <v>236.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>7.18</v>
+      </c>
+      <c r="L34">
+        <v>-7.18</v>
+      </c>
+      <c r="M34">
+        <v>44.50467840000001</v>
+      </c>
+      <c r="N34">
+        <v>-51.68467840000001</v>
+      </c>
+      <c r="O34">
+        <v>-12.9211696</v>
+      </c>
+      <c r="P34">
+        <v>-38.76350880000001</v>
+      </c>
+      <c r="Q34">
+        <v>-31.58350880000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09267766575002699</v>
+      </c>
+      <c r="T34">
+        <v>0.7962713250484341</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.04033283835615807</v>
+      </c>
+      <c r="W34">
+        <v>0.2484314817994506</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.1613313534246323</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1445188868858425</v>
+      </c>
+      <c r="C35">
+        <v>91.32928516824538</v>
+      </c>
+      <c r="D35">
+        <v>126.9212851682454</v>
+      </c>
+      <c r="E35">
+        <v>-153.908</v>
+      </c>
+      <c r="F35">
+        <v>192.192</v>
+      </c>
+      <c r="G35">
+        <v>156.6</v>
+      </c>
+      <c r="H35">
+        <v>236.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>7.18</v>
+      </c>
+      <c r="L35">
+        <v>-7.18</v>
+      </c>
+      <c r="M35">
+        <v>45.89544960000001</v>
+      </c>
+      <c r="N35">
+        <v>-53.07544960000001</v>
+      </c>
+      <c r="O35">
+        <v>-13.2688624</v>
+      </c>
+      <c r="P35">
+        <v>-39.80658720000001</v>
+      </c>
+      <c r="Q35">
+        <v>-32.62658720000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09348181001495277</v>
+      </c>
+      <c r="T35">
+        <v>0.8081559716909481</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.03911063113324419</v>
+      </c>
+      <c r="W35">
+        <v>0.2481396187146187</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.1564425245329768</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1465188868858426</v>
+      </c>
+      <c r="C36">
+        <v>83.14875719367106</v>
+      </c>
+      <c r="D36">
+        <v>124.5647571936711</v>
+      </c>
+      <c r="E36">
+        <v>-148.084</v>
+      </c>
+      <c r="F36">
+        <v>198.016</v>
+      </c>
+      <c r="G36">
+        <v>156.6</v>
+      </c>
+      <c r="H36">
+        <v>236.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>7.18</v>
+      </c>
+      <c r="L36">
+        <v>-7.18</v>
+      </c>
+      <c r="M36">
+        <v>47.28622080000002</v>
+      </c>
+      <c r="N36">
+        <v>-54.46622080000002</v>
+      </c>
+      <c r="O36">
+        <v>-13.6165552</v>
+      </c>
+      <c r="P36">
+        <v>-40.84966560000001</v>
+      </c>
+      <c r="Q36">
+        <v>-33.66966560000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.0943103222879066</v>
+      </c>
+      <c r="T36">
+        <v>0.820400759140811</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.03796031845285465</v>
+      </c>
+      <c r="W36">
+        <v>0.2478649240465417</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.1518412738114185</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1485188868858425</v>
+      </c>
+      <c r="C37">
+        <v>75.05414069856803</v>
+      </c>
+      <c r="D37">
+        <v>122.2941406985681</v>
+      </c>
+      <c r="E37">
+        <v>-142.26</v>
+      </c>
+      <c r="F37">
+        <v>203.8400000000001</v>
+      </c>
+      <c r="G37">
+        <v>156.6</v>
+      </c>
+      <c r="H37">
+        <v>236.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>7.18</v>
+      </c>
+      <c r="L37">
+        <v>-7.18</v>
+      </c>
+      <c r="M37">
+        <v>48.67699200000002</v>
+      </c>
+      <c r="N37">
+        <v>-55.85699200000002</v>
+      </c>
+      <c r="O37">
+        <v>-13.964248</v>
+      </c>
+      <c r="P37">
+        <v>-41.89274400000001</v>
+      </c>
+      <c r="Q37">
+        <v>-34.71274400000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.0951643272461821</v>
+      </c>
+      <c r="T37">
+        <v>0.8330223092814389</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.03687573792563023</v>
+      </c>
+      <c r="W37">
+        <v>0.2476059262166405</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.1475029517025208</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1505188868858425</v>
+      </c>
+      <c r="C38">
+        <v>67.04082170144036</v>
+      </c>
+      <c r="D38">
+        <v>120.1048217014404</v>
+      </c>
+      <c r="E38">
+        <v>-136.436</v>
+      </c>
+      <c r="F38">
+        <v>209.664</v>
+      </c>
+      <c r="G38">
+        <v>156.6</v>
+      </c>
+      <c r="H38">
+        <v>236.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>7.18</v>
+      </c>
+      <c r="L38">
+        <v>-7.18</v>
+      </c>
+      <c r="M38">
+        <v>50.06776320000001</v>
+      </c>
+      <c r="N38">
+        <v>-57.24776320000001</v>
+      </c>
+      <c r="O38">
+        <v>-14.3119408</v>
+      </c>
+      <c r="P38">
+        <v>-42.93582240000001</v>
+      </c>
+      <c r="Q38">
+        <v>-35.75582240000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.09604501985940368</v>
+      </c>
+      <c r="T38">
+        <v>0.8460382828639613</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.03585141187214051</v>
+      </c>
+      <c r="W38">
+        <v>0.2473613171550672</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.1434056474885621</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1525188868858425</v>
+      </c>
+      <c r="C39">
+        <v>59.10451080937176</v>
+      </c>
+      <c r="D39">
+        <v>117.9925108093718</v>
+      </c>
+      <c r="E39">
+        <v>-130.612</v>
+      </c>
+      <c r="F39">
+        <v>215.488</v>
+      </c>
+      <c r="G39">
+        <v>156.6</v>
+      </c>
+      <c r="H39">
+        <v>236.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>7.18</v>
+      </c>
+      <c r="L39">
+        <v>-7.18</v>
+      </c>
+      <c r="M39">
+        <v>51.45853440000001</v>
+      </c>
+      <c r="N39">
+        <v>-58.63853440000001</v>
+      </c>
+      <c r="O39">
+        <v>-14.6596336</v>
+      </c>
+      <c r="P39">
+        <v>-43.97890080000001</v>
+      </c>
+      <c r="Q39">
+        <v>-36.79890080000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.09695367096828311</v>
+      </c>
+      <c r="T39">
+        <v>0.85946746195704</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.03488245479451509</v>
+      </c>
+      <c r="W39">
+        <v>0.2471299302049302</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.1395298191780603</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1545188868858425</v>
+      </c>
+      <c r="C40">
+        <v>51.24121516827606</v>
+      </c>
+      <c r="D40">
+        <v>115.9532151682761</v>
+      </c>
+      <c r="E40">
+        <v>-124.788</v>
+      </c>
+      <c r="F40">
+        <v>221.312</v>
+      </c>
+      <c r="G40">
+        <v>156.6</v>
+      </c>
+      <c r="H40">
+        <v>236.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>7.18</v>
+      </c>
+      <c r="L40">
+        <v>-7.18</v>
+      </c>
+      <c r="M40">
+        <v>52.84930560000002</v>
+      </c>
+      <c r="N40">
+        <v>-60.02930560000001</v>
+      </c>
+      <c r="O40">
+        <v>-15.0073264</v>
+      </c>
+      <c r="P40">
+        <v>-45.02197920000001</v>
+      </c>
+      <c r="Q40">
+        <v>-37.84197920000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.09789163340325542</v>
+      </c>
+      <c r="T40">
+        <v>0.873329840375702</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.03396449545781732</v>
+      </c>
+      <c r="W40">
+        <v>0.2469107215153268</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.1358579818312693</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1565188868858425</v>
+      </c>
+      <c r="C41">
+        <v>43.44721327247626</v>
+      </c>
+      <c r="D41">
+        <v>113.9832132724763</v>
+      </c>
+      <c r="E41">
+        <v>-118.964</v>
+      </c>
+      <c r="F41">
+        <v>227.1360000000001</v>
+      </c>
+      <c r="G41">
+        <v>156.6</v>
+      </c>
+      <c r="H41">
+        <v>236.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>7.18</v>
+      </c>
+      <c r="L41">
+        <v>-7.18</v>
+      </c>
+      <c r="M41">
+        <v>54.24007680000002</v>
+      </c>
+      <c r="N41">
+        <v>-61.42007680000002</v>
+      </c>
+      <c r="O41">
+        <v>-15.3550192</v>
+      </c>
+      <c r="P41">
+        <v>-46.06505760000002</v>
+      </c>
+      <c r="Q41">
+        <v>-38.88505760000002</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.09886034870494811</v>
+      </c>
+      <c r="T41">
+        <v>0.8876467230048118</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.03309361095889893</v>
+      </c>
+      <c r="W41">
+        <v>0.246702754296985</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.1323744438355956</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1585188868858425</v>
+      </c>
+      <c r="C42">
+        <v>35.71903229924078</v>
+      </c>
+      <c r="D42">
+        <v>112.0790322992408</v>
+      </c>
+      <c r="E42">
+        <v>-113.14</v>
+      </c>
+      <c r="F42">
+        <v>232.96</v>
+      </c>
+      <c r="G42">
+        <v>156.6</v>
+      </c>
+      <c r="H42">
+        <v>236.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>7.18</v>
+      </c>
+      <c r="L42">
+        <v>-7.18</v>
+      </c>
+      <c r="M42">
+        <v>55.63084800000001</v>
+      </c>
+      <c r="N42">
+        <v>-62.81084800000001</v>
+      </c>
+      <c r="O42">
+        <v>-15.702712</v>
+      </c>
+      <c r="P42">
+        <v>-47.10813600000001</v>
+      </c>
+      <c r="Q42">
+        <v>-39.92813600000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.09986135451669727</v>
+      </c>
+      <c r="T42">
+        <v>0.9024408350548921</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.03226627068492646</v>
+      </c>
+      <c r="W42">
+        <v>0.2465051854395604</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.1290650827397057</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1605188868858425</v>
+      </c>
+      <c r="C43">
+        <v>28.05342767785845</v>
+      </c>
+      <c r="D43">
+        <v>110.2374276778585</v>
+      </c>
+      <c r="E43">
+        <v>-107.316</v>
+      </c>
+      <c r="F43">
+        <v>238.784</v>
+      </c>
+      <c r="G43">
+        <v>156.6</v>
+      </c>
+      <c r="H43">
+        <v>236.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>7.18</v>
+      </c>
+      <c r="L43">
+        <v>-7.18</v>
+      </c>
+      <c r="M43">
+        <v>57.02161920000002</v>
+      </c>
+      <c r="N43">
+        <v>-64.20161920000001</v>
+      </c>
+      <c r="O43">
+        <v>-16.0504048</v>
+      </c>
+      <c r="P43">
+        <v>-48.15121440000001</v>
+      </c>
+      <c r="Q43">
+        <v>-40.97121440000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1008962927288447</v>
+      </c>
+      <c r="T43">
+        <v>0.9177364424287038</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.03147928847309898</v>
+      </c>
+      <c r="W43">
+        <v>0.2463172540873761</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.1259171538923958</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1625188868858425</v>
+      </c>
+      <c r="C44">
+        <v>20.44736464039229</v>
+      </c>
+      <c r="D44">
+        <v>108.4553646403923</v>
+      </c>
+      <c r="E44">
+        <v>-101.492</v>
+      </c>
+      <c r="F44">
+        <v>244.608</v>
+      </c>
+      <c r="G44">
+        <v>156.6</v>
+      </c>
+      <c r="H44">
+        <v>236.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>7.18</v>
+      </c>
+      <c r="L44">
+        <v>-7.18</v>
+      </c>
+      <c r="M44">
+        <v>58.41239040000001</v>
+      </c>
+      <c r="N44">
+        <v>-65.59239040000001</v>
+      </c>
+      <c r="O44">
+        <v>-16.3980976</v>
+      </c>
+      <c r="P44">
+        <v>-49.19429280000001</v>
+      </c>
+      <c r="Q44">
+        <v>-42.01429280000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1019669184655489</v>
+      </c>
+      <c r="T44">
+        <v>0.9335594845395435</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.03072978160469186</v>
+      </c>
+      <c r="W44">
+        <v>0.2461382718472004</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.1229191264187675</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1645188868858425</v>
+      </c>
+      <c r="C45">
+        <v>12.89800153343324</v>
+      </c>
+      <c r="D45">
+        <v>106.7300015334333</v>
+      </c>
+      <c r="E45">
+        <v>-95.66799999999998</v>
+      </c>
+      <c r="F45">
+        <v>250.432</v>
+      </c>
+      <c r="G45">
+        <v>156.6</v>
+      </c>
+      <c r="H45">
+        <v>236.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>7.18</v>
+      </c>
+      <c r="L45">
+        <v>-7.18</v>
+      </c>
+      <c r="M45">
+        <v>59.80316160000002</v>
+      </c>
+      <c r="N45">
+        <v>-66.98316160000002</v>
+      </c>
+      <c r="O45">
+        <v>-16.7457904</v>
+      </c>
+      <c r="P45">
+        <v>-50.23737120000001</v>
+      </c>
+      <c r="Q45">
+        <v>-43.05737120000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1030751100175761</v>
+      </c>
+      <c r="T45">
+        <v>0.9499377211104126</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.03001513552086182</v>
+      </c>
+      <c r="W45">
+        <v>0.2459676143623818</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.1200605420834473</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1665188868858425</v>
+      </c>
+      <c r="C46">
+        <v>5.402674697820771</v>
+      </c>
+      <c r="D46">
+        <v>105.0586746978208</v>
+      </c>
+      <c r="E46">
+        <v>-89.84399999999999</v>
+      </c>
+      <c r="F46">
+        <v>256.256</v>
+      </c>
+      <c r="G46">
+        <v>156.6</v>
+      </c>
+      <c r="H46">
+        <v>236.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>7.18</v>
+      </c>
+      <c r="L46">
+        <v>-7.18</v>
+      </c>
+      <c r="M46">
+        <v>61.19393280000001</v>
+      </c>
+      <c r="N46">
+        <v>-68.37393280000001</v>
+      </c>
+      <c r="O46">
+        <v>-17.0934832</v>
+      </c>
+      <c r="P46">
+        <v>-51.2804496</v>
+      </c>
+      <c r="Q46">
+        <v>-44.1004496</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1042228798393185</v>
+      </c>
+      <c r="T46">
+        <v>0.9669008947016701</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.02933297334993314</v>
+      </c>
+      <c r="W46">
+        <v>0.2458047140359641</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.1173318933997325</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1685188868858425</v>
+      </c>
+      <c r="C47">
+        <v>-2.041115252894372</v>
+      </c>
+      <c r="D47">
+        <v>103.4388847471057</v>
+      </c>
+      <c r="E47">
+        <v>-84.01999999999998</v>
+      </c>
+      <c r="F47">
+        <v>262.08</v>
+      </c>
+      <c r="G47">
+        <v>156.6</v>
+      </c>
+      <c r="H47">
+        <v>236.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>7.18</v>
+      </c>
+      <c r="L47">
+        <v>-7.18</v>
+      </c>
+      <c r="M47">
+        <v>62.58470400000002</v>
+      </c>
+      <c r="N47">
+        <v>-69.76470400000002</v>
+      </c>
+      <c r="O47">
+        <v>-17.44117600000001</v>
+      </c>
+      <c r="P47">
+        <v>-52.32352800000002</v>
+      </c>
+      <c r="Q47">
+        <v>-45.14352800000002</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1054123867454879</v>
+      </c>
+      <c r="T47">
+        <v>0.9844809109689733</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.0286811294977124</v>
+      </c>
+      <c r="W47">
+        <v>0.2456490537240538</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.1147245179908498</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1705188868858425</v>
+      </c>
+      <c r="C48">
+        <v>-9.435715903911955</v>
+      </c>
+      <c r="D48">
+        <v>101.8682840960881</v>
+      </c>
+      <c r="E48">
+        <v>-78.19599999999997</v>
+      </c>
+      <c r="F48">
+        <v>267.9040000000001</v>
+      </c>
+      <c r="G48">
+        <v>156.6</v>
+      </c>
+      <c r="H48">
+        <v>236.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>7.18</v>
+      </c>
+      <c r="L48">
+        <v>-7.18</v>
+      </c>
+      <c r="M48">
+        <v>63.97547520000002</v>
+      </c>
+      <c r="N48">
+        <v>-71.15547520000001</v>
+      </c>
+      <c r="O48">
+        <v>-17.7888688</v>
+      </c>
+      <c r="P48">
+        <v>-53.36660640000001</v>
+      </c>
+      <c r="Q48">
+        <v>-46.18660640000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.106645949462997</v>
+      </c>
+      <c r="T48">
+        <v>1.00271203894988</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.02805762668254474</v>
+      </c>
+      <c r="W48">
+        <v>0.2455001612517917</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.1122305067301788</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1725188868858425</v>
+      </c>
+      <c r="C49">
+        <v>-16.78333439144922</v>
+      </c>
+      <c r="D49">
+        <v>100.3446656085508</v>
+      </c>
+      <c r="E49">
+        <v>-72.37199999999996</v>
+      </c>
+      <c r="F49">
+        <v>273.7280000000001</v>
+      </c>
+      <c r="G49">
+        <v>156.6</v>
+      </c>
+      <c r="H49">
+        <v>236.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>7.18</v>
+      </c>
+      <c r="L49">
+        <v>-7.18</v>
+      </c>
+      <c r="M49">
+        <v>65.36624640000002</v>
+      </c>
+      <c r="N49">
+        <v>-72.54624640000003</v>
+      </c>
+      <c r="O49">
+        <v>-18.13656160000001</v>
+      </c>
+      <c r="P49">
+        <v>-54.40968480000002</v>
+      </c>
+      <c r="Q49">
+        <v>-47.22968480000002</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1079260617170158</v>
+      </c>
+      <c r="T49">
+        <v>1.021631134024406</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.02746065590206507</v>
+      </c>
+      <c r="W49">
+        <v>0.2453576046294132</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.1098426236082604</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1745188868858426</v>
+      </c>
+      <c r="C50">
+        <v>-24.08604775126261</v>
+      </c>
+      <c r="D50">
+        <v>98.86595224873741</v>
+      </c>
+      <c r="E50">
+        <v>-66.548</v>
+      </c>
+      <c r="F50">
+        <v>279.552</v>
+      </c>
+      <c r="G50">
+        <v>156.6</v>
+      </c>
+      <c r="H50">
+        <v>236.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>7.18</v>
+      </c>
+      <c r="L50">
+        <v>-7.18</v>
+      </c>
+      <c r="M50">
+        <v>66.75701760000001</v>
+      </c>
+      <c r="N50">
+        <v>-73.93701760000002</v>
+      </c>
+      <c r="O50">
+        <v>-18.4842544</v>
+      </c>
+      <c r="P50">
+        <v>-55.45276320000001</v>
+      </c>
+      <c r="Q50">
+        <v>-48.27276320000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1092554090577276</v>
+      </c>
+      <c r="T50">
+        <v>1.041277886601799</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.02688855890410538</v>
+      </c>
+      <c r="W50">
+        <v>0.2452209878663004</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.1075542356164216</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1765188868858425</v>
+      </c>
+      <c r="C51">
+        <v>-31.34581236546094</v>
+      </c>
+      <c r="D51">
+        <v>97.4301876345391</v>
+      </c>
+      <c r="E51">
+        <v>-60.72399999999999</v>
+      </c>
+      <c r="F51">
+        <v>285.376</v>
+      </c>
+      <c r="G51">
+        <v>156.6</v>
+      </c>
+      <c r="H51">
+        <v>236.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>7.18</v>
+      </c>
+      <c r="L51">
+        <v>-7.18</v>
+      </c>
+      <c r="M51">
+        <v>68.14778880000001</v>
+      </c>
+      <c r="N51">
+        <v>-75.32778880000001</v>
+      </c>
+      <c r="O51">
+        <v>-18.8319472</v>
+      </c>
+      <c r="P51">
+        <v>-56.49584160000001</v>
+      </c>
+      <c r="Q51">
+        <v>-49.31584160000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1106368876667027</v>
+      </c>
+      <c r="T51">
+        <v>1.061695100064579</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.0263398128040216</v>
+      </c>
+      <c r="W51">
+        <v>0.2450899472976004</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.1053592512160864</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1785188868858425</v>
+      </c>
+      <c r="C52">
+        <v>-38.56447259796261</v>
+      </c>
+      <c r="D52">
+        <v>96.03552740203745</v>
+      </c>
+      <c r="E52">
+        <v>-54.89999999999998</v>
+      </c>
+      <c r="F52">
+        <v>291.2</v>
+      </c>
+      <c r="G52">
+        <v>156.6</v>
+      </c>
+      <c r="H52">
+        <v>236.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>7.18</v>
+      </c>
+      <c r="L52">
+        <v>-7.18</v>
+      </c>
+      <c r="M52">
+        <v>69.53856000000002</v>
+      </c>
+      <c r="N52">
+        <v>-76.71856000000002</v>
+      </c>
+      <c r="O52">
+        <v>-19.17964000000001</v>
+      </c>
+      <c r="P52">
+        <v>-57.53892000000002</v>
+      </c>
+      <c r="Q52">
+        <v>-50.35892000000002</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1120736254200367</v>
+      </c>
+      <c r="T52">
+        <v>1.08292900206587</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.02581301654794116</v>
+      </c>
+      <c r="W52">
+        <v>0.2449641483516483</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.1032520661917649</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1805188868858426</v>
+      </c>
+      <c r="C53">
+        <v>-45.74376869874834</v>
+      </c>
+      <c r="D53">
+        <v>94.68023130125171</v>
+      </c>
+      <c r="E53">
+        <v>-49.07599999999996</v>
+      </c>
+      <c r="F53">
+        <v>297.0240000000001</v>
+      </c>
+      <c r="G53">
+        <v>156.6</v>
+      </c>
+      <c r="H53">
+        <v>236.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>7.18</v>
+      </c>
+      <c r="L53">
+        <v>-7.18</v>
+      </c>
+      <c r="M53">
+        <v>70.92933120000002</v>
+      </c>
+      <c r="N53">
+        <v>-78.10933120000001</v>
+      </c>
+      <c r="O53">
+        <v>-19.5273328</v>
+      </c>
+      <c r="P53">
+        <v>-58.58199840000001</v>
+      </c>
+      <c r="Q53">
+        <v>-51.40199840000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1135690055306497</v>
+      </c>
+      <c r="T53">
+        <v>1.105029593944766</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.02530687896856977</v>
+      </c>
+      <c r="W53">
+        <v>0.2448432826976945</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.101227515874279</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1825188868858426</v>
+      </c>
+      <c r="C54">
+        <v>-52.88534404813799</v>
+      </c>
+      <c r="D54">
+        <v>93.36265595186207</v>
+      </c>
+      <c r="E54">
+        <v>-43.25199999999995</v>
+      </c>
+      <c r="F54">
+        <v>302.8480000000001</v>
+      </c>
+      <c r="G54">
+        <v>156.6</v>
+      </c>
+      <c r="H54">
+        <v>236.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>7.18</v>
+      </c>
+      <c r="L54">
+        <v>-7.18</v>
+      </c>
+      <c r="M54">
+        <v>72.32010240000002</v>
+      </c>
+      <c r="N54">
+        <v>-79.50010240000003</v>
+      </c>
+      <c r="O54">
+        <v>-19.87502560000001</v>
+      </c>
+      <c r="P54">
+        <v>-59.62507680000002</v>
+      </c>
+      <c r="Q54">
+        <v>-52.44507680000002</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1151266931458716</v>
+      </c>
+      <c r="T54">
+        <v>1.128051043818615</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.02482020821917419</v>
+      </c>
+      <c r="W54">
+        <v>0.2447270657227388</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.09928083287669698</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1845188868858425</v>
+      </c>
+      <c r="C55">
+        <v>-59.99075180449836</v>
+      </c>
+      <c r="D55">
+        <v>92.08124819550173</v>
+      </c>
+      <c r="E55">
+        <v>-37.42799999999994</v>
+      </c>
+      <c r="F55">
+        <v>308.6720000000001</v>
+      </c>
+      <c r="G55">
+        <v>156.6</v>
+      </c>
+      <c r="H55">
+        <v>236.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>7.18</v>
+      </c>
+      <c r="L55">
+        <v>-7.18</v>
+      </c>
+      <c r="M55">
+        <v>73.71087360000003</v>
+      </c>
+      <c r="N55">
+        <v>-80.89087360000002</v>
+      </c>
+      <c r="O55">
+        <v>-20.22271840000001</v>
+      </c>
+      <c r="P55">
+        <v>-60.66815520000002</v>
+      </c>
+      <c r="Q55">
+        <v>-53.48815520000002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1167506653404646</v>
+      </c>
+      <c r="T55">
+        <v>1.152052129857309</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.02435190240371807</v>
+      </c>
+      <c r="W55">
+        <v>0.2446152342940079</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.09740760961487216</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1865188868858426</v>
+      </c>
+      <c r="C56">
+        <v>-67.06146101192243</v>
+      </c>
+      <c r="D56">
+        <v>90.83453898807767</v>
+      </c>
+      <c r="E56">
+        <v>-31.60399999999993</v>
+      </c>
+      <c r="F56">
+        <v>314.4960000000001</v>
+      </c>
+      <c r="G56">
+        <v>156.6</v>
+      </c>
+      <c r="H56">
+        <v>236.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>7.18</v>
+      </c>
+      <c r="L56">
+        <v>-7.18</v>
+      </c>
+      <c r="M56">
+        <v>75.10164480000003</v>
+      </c>
+      <c r="N56">
+        <v>-82.28164480000004</v>
+      </c>
+      <c r="O56">
+        <v>-20.57041120000001</v>
+      </c>
+      <c r="P56">
+        <v>-61.71123360000003</v>
+      </c>
+      <c r="Q56">
+        <v>-54.53123360000003</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.118445245021779</v>
+      </c>
+      <c r="T56">
+        <v>1.177096741375946</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.02390094124809367</v>
+      </c>
+      <c r="W56">
+        <v>0.2445075447700448</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.09560376499237466</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1885188868858426</v>
+      </c>
+      <c r="C57">
+        <v>-74.09886221837587</v>
+      </c>
+      <c r="D57">
+        <v>89.62113778162417</v>
+      </c>
+      <c r="E57">
+        <v>-25.77999999999997</v>
+      </c>
+      <c r="F57">
+        <v>320.3200000000001</v>
+      </c>
+      <c r="G57">
+        <v>156.6</v>
+      </c>
+      <c r="H57">
+        <v>236.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>7.18</v>
+      </c>
+      <c r="L57">
+        <v>-7.18</v>
+      </c>
+      <c r="M57">
+        <v>76.49241600000002</v>
+      </c>
+      <c r="N57">
+        <v>-83.67241600000003</v>
+      </c>
+      <c r="O57">
+        <v>-20.91810400000001</v>
+      </c>
+      <c r="P57">
+        <v>-62.75431200000002</v>
+      </c>
+      <c r="Q57">
+        <v>-55.57431200000002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1202151393555964</v>
+      </c>
+      <c r="T57">
+        <v>1.203254446739856</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.02346637867994651</v>
+      </c>
+      <c r="W57">
+        <v>0.2444037712287712</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.09386551471978621</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1905188868858425</v>
+      </c>
+      <c r="C58">
+        <v>-81.10427264948532</v>
+      </c>
+      <c r="D58">
+        <v>88.43972735051474</v>
+      </c>
+      <c r="E58">
+        <v>-19.95599999999996</v>
+      </c>
+      <c r="F58">
+        <v>326.1440000000001</v>
+      </c>
+      <c r="G58">
+        <v>156.6</v>
+      </c>
+      <c r="H58">
+        <v>236.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>7.18</v>
+      </c>
+      <c r="L58">
+        <v>-7.18</v>
+      </c>
+      <c r="M58">
+        <v>77.88318720000002</v>
+      </c>
+      <c r="N58">
+        <v>-85.06318720000002</v>
+      </c>
+      <c r="O58">
+        <v>-21.2657968</v>
+      </c>
+      <c r="P58">
+        <v>-63.79739040000001</v>
+      </c>
+      <c r="Q58">
+        <v>-56.61739040000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1220654834318599</v>
+      </c>
+      <c r="T58">
+        <v>1.230601138711216</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.02304733620351889</v>
+      </c>
+      <c r="W58">
+        <v>0.2443037038854003</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.09218934481407559</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1925188868858426</v>
+      </c>
+      <c r="C59">
+        <v>-88.07894097843564</v>
+      </c>
+      <c r="D59">
+        <v>87.28905902156444</v>
+      </c>
+      <c r="E59">
+        <v>-14.13199999999995</v>
+      </c>
+      <c r="F59">
+        <v>331.9680000000001</v>
+      </c>
+      <c r="G59">
+        <v>156.6</v>
+      </c>
+      <c r="H59">
+        <v>236.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>7.18</v>
+      </c>
+      <c r="L59">
+        <v>-7.18</v>
+      </c>
+      <c r="M59">
+        <v>79.27395840000003</v>
+      </c>
+      <c r="N59">
+        <v>-86.45395840000003</v>
+      </c>
+      <c r="O59">
+        <v>-21.61348960000001</v>
+      </c>
+      <c r="P59">
+        <v>-64.84046880000002</v>
+      </c>
+      <c r="Q59">
+        <v>-57.66046880000003</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1240018900232985</v>
+      </c>
+      <c r="T59">
+        <v>1.259219769844036</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.02264299697187821</v>
+      </c>
+      <c r="W59">
+        <v>0.2442071476768845</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.09057198788751286</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1945188868858425</v>
+      </c>
+      <c r="C60">
+        <v>-95.02405172829026</v>
+      </c>
+      <c r="D60">
+        <v>86.16794827170979</v>
+      </c>
+      <c r="E60">
+        <v>-8.307999999999993</v>
+      </c>
+      <c r="F60">
+        <v>337.792</v>
+      </c>
+      <c r="G60">
+        <v>156.6</v>
+      </c>
+      <c r="H60">
+        <v>236.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>7.18</v>
+      </c>
+      <c r="L60">
+        <v>-7.18</v>
+      </c>
+      <c r="M60">
+        <v>80.66472960000002</v>
+      </c>
+      <c r="N60">
+        <v>-87.84472960000002</v>
+      </c>
+      <c r="O60">
+        <v>-21.96118240000001</v>
+      </c>
+      <c r="P60">
+        <v>-65.88354720000001</v>
+      </c>
+      <c r="Q60">
+        <v>-58.70354720000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1260305064524246</v>
+      </c>
+      <c r="T60">
+        <v>1.28920119293556</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.02225260047236307</v>
+      </c>
+      <c r="W60">
+        <v>0.2441139209928003</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.08901040188945242</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1965188868858425</v>
+      </c>
+      <c r="C61">
+        <v>-101.9407293393627</v>
+      </c>
+      <c r="D61">
+        <v>85.07527066063737</v>
+      </c>
+      <c r="E61">
+        <v>-2.48399999999998</v>
+      </c>
+      <c r="F61">
+        <v>343.616</v>
+      </c>
+      <c r="G61">
+        <v>156.6</v>
+      </c>
+      <c r="H61">
+        <v>236.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>7.18</v>
+      </c>
+      <c r="L61">
+        <v>-7.18</v>
+      </c>
+      <c r="M61">
+        <v>82.05550080000002</v>
+      </c>
+      <c r="N61">
+        <v>-89.23550080000001</v>
+      </c>
+      <c r="O61">
+        <v>-22.3088752</v>
+      </c>
+      <c r="P61">
+        <v>-66.92662560000001</v>
+      </c>
+      <c r="Q61">
+        <v>-59.74662560000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1281580797805326</v>
+      </c>
+      <c r="T61">
+        <v>1.320645124470574</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.02187543775249251</v>
+      </c>
+      <c r="W61">
+        <v>0.2440238545352952</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.08750175100997004</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1985188868858425</v>
+      </c>
+      <c r="C62">
+        <v>-108.8300419309968</v>
+      </c>
+      <c r="D62">
+        <v>84.00995806900323</v>
+      </c>
+      <c r="E62">
+        <v>3.340000000000032</v>
+      </c>
+      <c r="F62">
+        <v>349.4400000000001</v>
+      </c>
+      <c r="G62">
+        <v>156.6</v>
+      </c>
+      <c r="H62">
+        <v>236.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>7.18</v>
+      </c>
+      <c r="L62">
+        <v>-7.18</v>
+      </c>
+      <c r="M62">
+        <v>83.44627200000002</v>
+      </c>
+      <c r="N62">
+        <v>-90.62627200000003</v>
+      </c>
+      <c r="O62">
+        <v>-22.65656800000001</v>
+      </c>
+      <c r="P62">
+        <v>-67.96970400000002</v>
+      </c>
+      <c r="Q62">
+        <v>-60.78970400000002</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1303920317750459</v>
+      </c>
+      <c r="T62">
+        <v>1.353661252582338</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.0215108471232843</v>
+      </c>
+      <c r="W62">
+        <v>0.2439367902930403</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.08604338849313731</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2005188868858426</v>
+      </c>
+      <c r="C63">
+        <v>-115.6930047842139</v>
+      </c>
+      <c r="D63">
+        <v>82.97099521578613</v>
+      </c>
+      <c r="E63">
+        <v>9.164000000000044</v>
+      </c>
+      <c r="F63">
+        <v>355.2640000000001</v>
+      </c>
+      <c r="G63">
+        <v>156.6</v>
+      </c>
+      <c r="H63">
+        <v>236.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>7.18</v>
+      </c>
+      <c r="L63">
+        <v>-7.18</v>
+      </c>
+      <c r="M63">
+        <v>84.83704320000002</v>
+      </c>
+      <c r="N63">
+        <v>-92.01704320000002</v>
+      </c>
+      <c r="O63">
+        <v>-23.0042608</v>
+      </c>
+      <c r="P63">
+        <v>-69.01278240000002</v>
+      </c>
+      <c r="Q63">
+        <v>-61.83278240000002</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1327405454103035</v>
+      </c>
+      <c r="T63">
+        <v>1.388370515469065</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.02115821028519767</v>
+      </c>
+      <c r="W63">
+        <v>0.2438525806161052</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.08463284114079062</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2025188868858425</v>
+      </c>
+      <c r="C64">
+        <v>-122.5305835690934</v>
+      </c>
+      <c r="D64">
+        <v>81.95741643090665</v>
+      </c>
+      <c r="E64">
+        <v>14.98800000000006</v>
+      </c>
+      <c r="F64">
+        <v>361.0880000000001</v>
+      </c>
+      <c r="G64">
+        <v>156.6</v>
+      </c>
+      <c r="H64">
+        <v>236.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>7.18</v>
+      </c>
+      <c r="L64">
+        <v>-7.18</v>
+      </c>
+      <c r="M64">
+        <v>86.22781440000003</v>
+      </c>
+      <c r="N64">
+        <v>-93.40781440000003</v>
+      </c>
+      <c r="O64">
+        <v>-23.35195360000001</v>
+      </c>
+      <c r="P64">
+        <v>-70.05586080000003</v>
+      </c>
+      <c r="Q64">
+        <v>-62.87586080000003</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1352126650263641</v>
+      </c>
+      <c r="T64">
+        <v>1.424906581665619</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.02081694882898481</v>
+      </c>
+      <c r="W64">
+        <v>0.2437710873803616</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.08326779531593931</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2045188868858426</v>
+      </c>
+      <c r="C65">
+        <v>-129.3436973384535</v>
+      </c>
+      <c r="D65">
+        <v>80.96830266154656</v>
+      </c>
+      <c r="E65">
+        <v>20.81200000000001</v>
+      </c>
+      <c r="F65">
+        <v>366.912</v>
+      </c>
+      <c r="G65">
+        <v>156.6</v>
+      </c>
+      <c r="H65">
+        <v>236.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>7.18</v>
+      </c>
+      <c r="L65">
+        <v>-7.18</v>
+      </c>
+      <c r="M65">
+        <v>87.61858560000002</v>
+      </c>
+      <c r="N65">
+        <v>-94.79858560000002</v>
+      </c>
+      <c r="O65">
+        <v>-23.69964640000001</v>
+      </c>
+      <c r="P65">
+        <v>-71.09893920000002</v>
+      </c>
+      <c r="Q65">
+        <v>-63.91893920000002</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1378184127297793</v>
+      </c>
+      <c r="T65">
+        <v>1.463417570359285</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.02048652106979458</v>
+      </c>
+      <c r="W65">
+        <v>0.243692181231467</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.08194608427917838</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2065188868858426</v>
+      </c>
+      <c r="C66">
+        <v>-136.1332213073391</v>
+      </c>
+      <c r="D66">
+        <v>80.00277869266098</v>
+      </c>
+      <c r="E66">
+        <v>26.63600000000002</v>
+      </c>
+      <c r="F66">
+        <v>372.736</v>
+      </c>
+      <c r="G66">
+        <v>156.6</v>
+      </c>
+      <c r="H66">
+        <v>236.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>7.18</v>
+      </c>
+      <c r="L66">
+        <v>-7.18</v>
+      </c>
+      <c r="M66">
+        <v>89.00935680000002</v>
+      </c>
+      <c r="N66">
+        <v>-96.18935680000001</v>
+      </c>
+      <c r="O66">
+        <v>-24.0473392</v>
+      </c>
+      <c r="P66">
+        <v>-72.1420176</v>
+      </c>
+      <c r="Q66">
+        <v>-64.9620176</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1405689241944955</v>
+      </c>
+      <c r="T66">
+        <v>1.50406805842482</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.02016641917807904</v>
+      </c>
+      <c r="W66">
+        <v>0.2436157408997253</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.08066567671231595</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2085188868858425</v>
+      </c>
+      <c r="C67">
+        <v>-142.8999894359855</v>
+      </c>
+      <c r="D67">
+        <v>79.06001056401455</v>
+      </c>
+      <c r="E67">
+        <v>32.46000000000004</v>
+      </c>
+      <c r="F67">
+        <v>378.5600000000001</v>
+      </c>
+      <c r="G67">
+        <v>156.6</v>
+      </c>
+      <c r="H67">
+        <v>236.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>7.18</v>
+      </c>
+      <c r="L67">
+        <v>-7.18</v>
+      </c>
+      <c r="M67">
+        <v>90.40012800000002</v>
+      </c>
+      <c r="N67">
+        <v>-97.58012800000003</v>
+      </c>
+      <c r="O67">
+        <v>-24.39503200000001</v>
+      </c>
+      <c r="P67">
+        <v>-73.18509600000002</v>
+      </c>
+      <c r="Q67">
+        <v>-66.00509600000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1434766077429096</v>
+      </c>
+      <c r="T67">
+        <v>1.547041431522672</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.01985616657533936</v>
+      </c>
+      <c r="W67">
+        <v>0.243541652578191</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.07942466630135758</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2105188868858426</v>
+      </c>
+      <c r="C68">
+        <v>-149.6447968322805</v>
+      </c>
+      <c r="D68">
+        <v>78.13920316771953</v>
+      </c>
+      <c r="E68">
+        <v>38.28400000000005</v>
+      </c>
+      <c r="F68">
+        <v>384.3840000000001</v>
+      </c>
+      <c r="G68">
+        <v>156.6</v>
+      </c>
+      <c r="H68">
+        <v>236.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>7.18</v>
+      </c>
+      <c r="L68">
+        <v>-7.18</v>
+      </c>
+      <c r="M68">
+        <v>91.79089920000003</v>
+      </c>
+      <c r="N68">
+        <v>-98.97089920000002</v>
+      </c>
+      <c r="O68">
+        <v>-24.7427248</v>
+      </c>
+      <c r="P68">
+        <v>-74.22817440000001</v>
+      </c>
+      <c r="Q68">
+        <v>-67.04817440000002</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.146555331500054</v>
+      </c>
+      <c r="T68">
+        <v>1.592542650096868</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.01955531556662209</v>
+      </c>
+      <c r="W68">
+        <v>0.2434698093573094</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.0782212622664884</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2125188868858425</v>
+      </c>
+      <c r="C69">
+        <v>-156.368401988271</v>
+      </c>
+      <c r="D69">
+        <v>77.23959801172903</v>
+      </c>
+      <c r="E69">
+        <v>44.10800000000006</v>
+      </c>
+      <c r="F69">
+        <v>390.2080000000001</v>
+      </c>
+      <c r="G69">
+        <v>156.6</v>
+      </c>
+      <c r="H69">
+        <v>236.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>7.18</v>
+      </c>
+      <c r="L69">
+        <v>-7.18</v>
+      </c>
+      <c r="M69">
+        <v>93.18167040000003</v>
+      </c>
+      <c r="N69">
+        <v>-100.3616704</v>
+      </c>
+      <c r="O69">
+        <v>-25.09041760000001</v>
+      </c>
+      <c r="P69">
+        <v>-75.27125280000003</v>
+      </c>
+      <c r="Q69">
+        <v>-68.09125280000003</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1498206445758132</v>
+      </c>
+      <c r="T69">
+        <v>1.640801518281622</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.01926344518503072</v>
+      </c>
+      <c r="W69">
+        <v>0.2434001107101853</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.07705378074012303</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2145188868858426</v>
+      </c>
+      <c r="C70">
+        <v>-163.0715288639371</v>
+      </c>
+      <c r="D70">
+        <v>76.36047113606301</v>
+      </c>
+      <c r="E70">
+        <v>49.93200000000007</v>
+      </c>
+      <c r="F70">
+        <v>396.0320000000001</v>
+      </c>
+      <c r="G70">
+        <v>156.6</v>
+      </c>
+      <c r="H70">
+        <v>236.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>7.18</v>
+      </c>
+      <c r="L70">
+        <v>-7.18</v>
+      </c>
+      <c r="M70">
+        <v>94.57244160000003</v>
+      </c>
+      <c r="N70">
+        <v>-101.7524416</v>
+      </c>
+      <c r="O70">
+        <v>-25.43811040000001</v>
+      </c>
+      <c r="P70">
+        <v>-76.31433120000003</v>
+      </c>
+      <c r="Q70">
+        <v>-69.13433120000002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1532900397188074</v>
+      </c>
+      <c r="T70">
+        <v>1.692076565727923</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.01898015922642732</v>
+      </c>
+      <c r="W70">
+        <v>0.2433324620232709</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.07592063690570927</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2165188868858426</v>
+      </c>
+      <c r="C71">
+        <v>-169.754868830264</v>
+      </c>
+      <c r="D71">
+        <v>75.50113116973614</v>
+      </c>
+      <c r="E71">
+        <v>55.75600000000009</v>
+      </c>
+      <c r="F71">
+        <v>401.8560000000001</v>
+      </c>
+      <c r="G71">
+        <v>156.6</v>
+      </c>
+      <c r="H71">
+        <v>236.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>7.18</v>
+      </c>
+      <c r="L71">
+        <v>-7.18</v>
+      </c>
+      <c r="M71">
+        <v>95.96321280000004</v>
+      </c>
+      <c r="N71">
+        <v>-103.1432128</v>
+      </c>
+      <c r="O71">
+        <v>-25.78580320000001</v>
+      </c>
+      <c r="P71">
+        <v>-77.35740960000004</v>
+      </c>
+      <c r="Q71">
+        <v>-70.17740960000003</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1569832668065109</v>
+      </c>
+      <c r="T71">
+        <v>1.746659680751405</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.01870508445502983</v>
+      </c>
+      <c r="W71">
+        <v>0.2432667741678611</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.07482033782011932</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2185188868858426</v>
+      </c>
+      <c r="C72">
+        <v>-176.4190824825741</v>
+      </c>
+      <c r="D72">
+        <v>74.660917517426</v>
+      </c>
+      <c r="E72">
+        <v>61.5800000000001</v>
+      </c>
+      <c r="F72">
+        <v>407.6800000000001</v>
+      </c>
+      <c r="G72">
+        <v>156.6</v>
+      </c>
+      <c r="H72">
+        <v>236.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>7.18</v>
+      </c>
+      <c r="L72">
+        <v>-7.18</v>
+      </c>
+      <c r="M72">
+        <v>97.35398400000004</v>
+      </c>
+      <c r="N72">
+        <v>-104.533984</v>
+      </c>
+      <c r="O72">
+        <v>-26.13349600000001</v>
+      </c>
+      <c r="P72">
+        <v>-78.40048800000002</v>
+      </c>
+      <c r="Q72">
+        <v>-71.22048800000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1609227090333946</v>
+      </c>
+      <c r="T72">
+        <v>1.804881670109785</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.01843786896281512</v>
+      </c>
+      <c r="W72">
+        <v>0.2432029631083203</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.0737514758512603</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2205188868858425</v>
+      </c>
+      <c r="C73">
+        <v>-183.0648013341134</v>
+      </c>
+      <c r="D73">
+        <v>73.83919866588658</v>
+      </c>
+      <c r="E73">
+        <v>67.404</v>
+      </c>
+      <c r="F73">
+        <v>413.504</v>
+      </c>
+      <c r="G73">
+        <v>156.6</v>
+      </c>
+      <c r="H73">
+        <v>236.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>7.18</v>
+      </c>
+      <c r="L73">
+        <v>-7.18</v>
+      </c>
+      <c r="M73">
+        <v>98.74475520000001</v>
+      </c>
+      <c r="N73">
+        <v>-105.9247552</v>
+      </c>
+      <c r="O73">
+        <v>-26.48118880000001</v>
+      </c>
+      <c r="P73">
+        <v>-79.44356640000001</v>
+      </c>
+      <c r="Q73">
+        <v>-72.2635664</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1651338369310978</v>
+      </c>
+      <c r="T73">
+        <v>1.867118969079087</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.0181781806675642</v>
+      </c>
+      <c r="W73">
+        <v>0.2431409495434144</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.07271272267025686</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2225188868858425</v>
+      </c>
+      <c r="C74">
+        <v>-189.6926293990175</v>
+      </c>
+      <c r="D74">
+        <v>73.03537060098256</v>
+      </c>
+      <c r="E74">
+        <v>73.22800000000001</v>
+      </c>
+      <c r="F74">
+        <v>419.328</v>
+      </c>
+      <c r="G74">
+        <v>156.6</v>
+      </c>
+      <c r="H74">
+        <v>236.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>7.18</v>
+      </c>
+      <c r="L74">
+        <v>-7.18</v>
+      </c>
+      <c r="M74">
+        <v>100.1355264</v>
+      </c>
+      <c r="N74">
+        <v>-107.3155264</v>
+      </c>
+      <c r="O74">
+        <v>-26.8288816</v>
+      </c>
+      <c r="P74">
+        <v>-80.48664480000001</v>
+      </c>
+      <c r="Q74">
+        <v>-73.30664480000002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.169645759678637</v>
+      </c>
+      <c r="T74">
+        <v>1.93380178940334</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.01792570593607025</v>
+      </c>
+      <c r="W74">
+        <v>0.2430806585775336</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.07170282374428094</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2245188868858425</v>
+      </c>
+      <c r="C75">
+        <v>-196.3031446729958</v>
+      </c>
+      <c r="D75">
+        <v>72.24885532700428</v>
+      </c>
+      <c r="E75">
+        <v>79.05200000000002</v>
+      </c>
+      <c r="F75">
+        <v>425.152</v>
+      </c>
+      <c r="G75">
+        <v>156.6</v>
+      </c>
+      <c r="H75">
+        <v>236.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>7.18</v>
+      </c>
+      <c r="L75">
+        <v>-7.18</v>
+      </c>
+      <c r="M75">
+        <v>101.5262976</v>
+      </c>
+      <c r="N75">
+        <v>-108.7062976</v>
+      </c>
+      <c r="O75">
+        <v>-27.17657440000001</v>
+      </c>
+      <c r="P75">
+        <v>-81.52972320000002</v>
+      </c>
+      <c r="Q75">
+        <v>-74.34972320000003</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1744918989259939</v>
+      </c>
+      <c r="T75">
+        <v>2.00542407789976</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.01768014832050765</v>
+      </c>
+      <c r="W75">
+        <v>0.2430220194189372</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.07072059328203073</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2265188868858425</v>
+      </c>
+      <c r="C76">
+        <v>-202.8969005193635</v>
+      </c>
+      <c r="D76">
+        <v>71.47909948063659</v>
+      </c>
+      <c r="E76">
+        <v>84.87600000000003</v>
+      </c>
+      <c r="F76">
+        <v>430.9760000000001</v>
+      </c>
+      <c r="G76">
+        <v>156.6</v>
+      </c>
+      <c r="H76">
+        <v>236.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>7.18</v>
+      </c>
+      <c r="L76">
+        <v>-7.18</v>
+      </c>
+      <c r="M76">
+        <v>102.9170688</v>
+      </c>
+      <c r="N76">
+        <v>-110.0970688</v>
+      </c>
+      <c r="O76">
+        <v>-27.5242672</v>
+      </c>
+      <c r="P76">
+        <v>-82.57280160000002</v>
+      </c>
+      <c r="Q76">
+        <v>-75.39280160000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1797108181154552</v>
+      </c>
+      <c r="T76">
+        <v>2.082555773203597</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.01744122739725754</v>
+      </c>
+      <c r="W76">
+        <v>0.2429649651024651</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.06976490958903003</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2285188868858425</v>
+      </c>
+      <c r="C77">
+        <v>-209.4744269674039</v>
+      </c>
+      <c r="D77">
+        <v>70.72557303259615</v>
+      </c>
+      <c r="E77">
+        <v>90.70000000000005</v>
+      </c>
+      <c r="F77">
+        <v>436.8000000000001</v>
+      </c>
+      <c r="G77">
+        <v>156.6</v>
+      </c>
+      <c r="H77">
+        <v>236.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>7.18</v>
+      </c>
+      <c r="L77">
+        <v>-7.18</v>
+      </c>
+      <c r="M77">
+        <v>104.30784</v>
+      </c>
+      <c r="N77">
+        <v>-111.48784</v>
+      </c>
+      <c r="O77">
+        <v>-27.87196000000001</v>
+      </c>
+      <c r="P77">
+        <v>-83.61588000000003</v>
+      </c>
+      <c r="Q77">
+        <v>-76.43588000000003</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1853472508400734</v>
+      </c>
+      <c r="T77">
+        <v>2.165858004131741</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.01720867769862744</v>
+      </c>
+      <c r="W77">
+        <v>0.2429094322344323</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.06883471079450976</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2305188868858425</v>
+      </c>
+      <c r="C78">
+        <v>-216.036231929465</v>
+      </c>
+      <c r="D78">
+        <v>69.9877680705351</v>
+      </c>
+      <c r="E78">
+        <v>96.52400000000006</v>
+      </c>
+      <c r="F78">
+        <v>442.6240000000001</v>
+      </c>
+      <c r="G78">
+        <v>156.6</v>
+      </c>
+      <c r="H78">
+        <v>236.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>7.18</v>
+      </c>
+      <c r="L78">
+        <v>-7.18</v>
+      </c>
+      <c r="M78">
+        <v>105.6986112</v>
+      </c>
+      <c r="N78">
+        <v>-112.8786112</v>
+      </c>
+      <c r="O78">
+        <v>-28.21965280000001</v>
+      </c>
+      <c r="P78">
+        <v>-84.65895840000002</v>
+      </c>
+      <c r="Q78">
+        <v>-77.47895840000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1914533862917432</v>
+      </c>
+      <c r="T78">
+        <v>2.25610208763723</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.01698224772890866</v>
+      </c>
+      <c r="W78">
+        <v>0.2428553607576634</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.06792899091563465</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2325188868858425</v>
+      </c>
+      <c r="C79">
+        <v>-222.5828023426615</v>
+      </c>
+      <c r="D79">
+        <v>69.26519765733859</v>
+      </c>
+      <c r="E79">
+        <v>102.3480000000001</v>
+      </c>
+      <c r="F79">
+        <v>448.4480000000001</v>
+      </c>
+      <c r="G79">
+        <v>156.6</v>
+      </c>
+      <c r="H79">
+        <v>236.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>7.18</v>
+      </c>
+      <c r="L79">
+        <v>-7.18</v>
+      </c>
+      <c r="M79">
+        <v>107.0893824</v>
+      </c>
+      <c r="N79">
+        <v>-114.2693824</v>
+      </c>
+      <c r="O79">
+        <v>-28.56734560000001</v>
+      </c>
+      <c r="P79">
+        <v>-85.70203680000003</v>
+      </c>
+      <c r="Q79">
+        <v>-78.52203680000002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1980904900435581</v>
+      </c>
+      <c r="T79">
+        <v>2.354193482751893</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.01676169905710465</v>
+      </c>
+      <c r="W79">
+        <v>0.2428026937348366</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.06704679622841869</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2345188868858426</v>
+      </c>
+      <c r="C80">
+        <v>-229.1146052405774</v>
+      </c>
+      <c r="D80">
+        <v>68.55739475942266</v>
+      </c>
+      <c r="E80">
+        <v>108.1720000000001</v>
+      </c>
+      <c r="F80">
+        <v>454.2720000000001</v>
+      </c>
+      <c r="G80">
+        <v>156.6</v>
+      </c>
+      <c r="H80">
+        <v>236.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>7.18</v>
+      </c>
+      <c r="L80">
+        <v>-7.18</v>
+      </c>
+      <c r="M80">
+        <v>108.4801536</v>
+      </c>
+      <c r="N80">
+        <v>-115.6601536</v>
+      </c>
+      <c r="O80">
+        <v>-28.91503840000001</v>
+      </c>
+      <c r="P80">
+        <v>-86.74511520000001</v>
+      </c>
+      <c r="Q80">
+        <v>-79.56511520000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2053309668637198</v>
+      </c>
+      <c r="T80">
+        <v>2.461202277422433</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.01654680547944946</v>
+      </c>
+      <c r="W80">
+        <v>0.2427513771484926</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.06618722191779769</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2365188868858425</v>
+      </c>
+      <c r="C81">
+        <v>-235.6320887599238</v>
+      </c>
+      <c r="D81">
+        <v>67.86391124007631</v>
+      </c>
+      <c r="E81">
+        <v>113.9960000000001</v>
+      </c>
+      <c r="F81">
+        <v>460.0960000000001</v>
+      </c>
+      <c r="G81">
+        <v>156.6</v>
+      </c>
+      <c r="H81">
+        <v>236.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>7.18</v>
+      </c>
+      <c r="L81">
+        <v>-7.18</v>
+      </c>
+      <c r="M81">
+        <v>109.8709248</v>
+      </c>
+      <c r="N81">
+        <v>-117.0509248</v>
+      </c>
+      <c r="O81">
+        <v>-29.26273120000001</v>
+      </c>
+      <c r="P81">
+        <v>-87.78819360000003</v>
+      </c>
+      <c r="Q81">
+        <v>-80.60819360000002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2132610129048494</v>
+      </c>
+      <c r="T81">
+        <v>2.578402385871121</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.01633735224553238</v>
+      </c>
+      <c r="W81">
+        <v>0.2427013597162331</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.0653494089821296</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2385188868858426</v>
+      </c>
+      <c r="C82">
+        <v>-242.1356830867124</v>
+      </c>
+      <c r="D82">
+        <v>67.18431691328769</v>
+      </c>
+      <c r="E82">
+        <v>119.8200000000001</v>
+      </c>
+      <c r="F82">
+        <v>465.9200000000001</v>
+      </c>
+      <c r="G82">
+        <v>156.6</v>
+      </c>
+      <c r="H82">
+        <v>236.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>7.18</v>
+      </c>
+      <c r="L82">
+        <v>-7.18</v>
+      </c>
+      <c r="M82">
+        <v>111.261696</v>
+      </c>
+      <c r="N82">
+        <v>-118.441696</v>
+      </c>
+      <c r="O82">
+        <v>-29.61042400000001</v>
+      </c>
+      <c r="P82">
+        <v>-88.83127200000003</v>
+      </c>
+      <c r="Q82">
+        <v>-81.65127200000003</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2219840635500918</v>
+      </c>
+      <c r="T82">
+        <v>2.707322505164677</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.01613313534246323</v>
+      </c>
+      <c r="W82">
+        <v>0.2426525927197802</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.06453254136985298</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2405188868858426</v>
+      </c>
+      <c r="C83">
+        <v>-248.6258013461425</v>
+      </c>
+      <c r="D83">
+        <v>66.51819865385755</v>
+      </c>
+      <c r="E83">
+        <v>125.6440000000001</v>
+      </c>
+      <c r="F83">
+        <v>471.7440000000001</v>
+      </c>
+      <c r="G83">
+        <v>156.6</v>
+      </c>
+      <c r="H83">
+        <v>236.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>7.18</v>
+      </c>
+      <c r="L83">
+        <v>-7.18</v>
+      </c>
+      <c r="M83">
+        <v>112.6524672</v>
+      </c>
+      <c r="N83">
+        <v>-119.8324672</v>
+      </c>
+      <c r="O83">
+        <v>-29.95811680000001</v>
+      </c>
+      <c r="P83">
+        <v>-89.87435040000003</v>
+      </c>
+      <c r="Q83">
+        <v>-82.69435040000002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2316253300527283</v>
+      </c>
+      <c r="T83">
+        <v>2.849813163331239</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.01593396083206245</v>
+      </c>
+      <c r="W83">
+        <v>0.2426050298466965</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.06373584332824977</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2425188868858425</v>
+      </c>
+      <c r="C84">
+        <v>-255.1028404400693</v>
+      </c>
+      <c r="D84">
+        <v>65.86515955993077</v>
+      </c>
+      <c r="E84">
+        <v>131.4680000000001</v>
+      </c>
+      <c r="F84">
+        <v>477.5680000000001</v>
+      </c>
+      <c r="G84">
+        <v>156.6</v>
+      </c>
+      <c r="H84">
+        <v>236.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>7.18</v>
+      </c>
+      <c r="L84">
+        <v>-7.18</v>
+      </c>
+      <c r="M84">
+        <v>114.0432384</v>
+      </c>
+      <c r="N84">
+        <v>-121.2232384</v>
+      </c>
+      <c r="O84">
+        <v>-30.30580960000001</v>
+      </c>
+      <c r="P84">
+        <v>-90.91742880000004</v>
+      </c>
+      <c r="Q84">
+        <v>-83.73742880000003</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2423378483889909</v>
+      </c>
+      <c r="T84">
+        <v>3.008136116849641</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.01573964423654949</v>
+      </c>
+      <c r="W84">
+        <v>0.242558627043688</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.062958576946198</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2445188868858426</v>
+      </c>
+      <c r="C85">
+        <v>-261.5671818356213</v>
+      </c>
+      <c r="D85">
+        <v>65.22481816437885</v>
+      </c>
+      <c r="E85">
+        <v>137.2920000000001</v>
+      </c>
+      <c r="F85">
+        <v>483.3920000000001</v>
+      </c>
+      <c r="G85">
+        <v>156.6</v>
+      </c>
+      <c r="H85">
+        <v>236.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>7.18</v>
+      </c>
+      <c r="L85">
+        <v>-7.18</v>
+      </c>
+      <c r="M85">
+        <v>115.4340096</v>
+      </c>
+      <c r="N85">
+        <v>-122.6140096</v>
+      </c>
+      <c r="O85">
+        <v>-30.65350240000001</v>
+      </c>
+      <c r="P85">
+        <v>-91.96050720000002</v>
+      </c>
+      <c r="Q85">
+        <v>-84.78050720000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2543106630001081</v>
+      </c>
+      <c r="T85">
+        <v>3.185085300193738</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.01555000996863925</v>
+      </c>
+      <c r="W85">
+        <v>0.2425133423805111</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.06220003987455702</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2465188868858425</v>
+      </c>
+      <c r="C86">
+        <v>-268.019192308258</v>
+      </c>
+      <c r="D86">
+        <v>64.59680769174213</v>
+      </c>
+      <c r="E86">
+        <v>143.116</v>
+      </c>
+      <c r="F86">
+        <v>489.2160000000001</v>
+      </c>
+      <c r="G86">
+        <v>156.6</v>
+      </c>
+      <c r="H86">
+        <v>236.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>7.18</v>
+      </c>
+      <c r="L86">
+        <v>-7.18</v>
+      </c>
+      <c r="M86">
+        <v>116.8247808</v>
+      </c>
+      <c r="N86">
+        <v>-124.0047808</v>
+      </c>
+      <c r="O86">
+        <v>-31.00119520000001</v>
+      </c>
+      <c r="P86">
+        <v>-93.00358560000001</v>
+      </c>
+      <c r="Q86">
+        <v>-85.8235856</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2677800794376147</v>
+      </c>
+      <c r="T86">
+        <v>3.384153131455844</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.01536489080234593</v>
+      </c>
+      <c r="W86">
+        <v>0.2424691359236002</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.06145956320938373</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2485188868858426</v>
+      </c>
+      <c r="C87">
+        <v>-274.4592246423119</v>
+      </c>
+      <c r="D87">
+        <v>63.98077535768816</v>
+      </c>
+      <c r="E87">
+        <v>148.9400000000001</v>
+      </c>
+      <c r="F87">
+        <v>495.0400000000001</v>
+      </c>
+      <c r="G87">
+        <v>156.6</v>
+      </c>
+      <c r="H87">
+        <v>236.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>7.18</v>
+      </c>
+      <c r="L87">
+        <v>-7.18</v>
+      </c>
+      <c r="M87">
+        <v>118.215552</v>
+      </c>
+      <c r="N87">
+        <v>-125.395552</v>
+      </c>
+      <c r="O87">
+        <v>-31.34888800000001</v>
+      </c>
+      <c r="P87">
+        <v>-94.04666400000002</v>
+      </c>
+      <c r="Q87">
+        <v>-86.86666400000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2830454180667891</v>
+      </c>
+      <c r="T87">
+        <v>3.609763340219568</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.01518412738114186</v>
+      </c>
+      <c r="W87">
+        <v>0.2424259696186167</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.06073650952456755</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2505188868858425</v>
+      </c>
+      <c r="C88">
+        <v>-280.8876182918231</v>
+      </c>
+      <c r="D88">
+        <v>63.37638170817699</v>
+      </c>
+      <c r="E88">
+        <v>154.7640000000001</v>
+      </c>
+      <c r="F88">
+        <v>500.8640000000001</v>
+      </c>
+      <c r="G88">
+        <v>156.6</v>
+      </c>
+      <c r="H88">
+        <v>236.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>7.18</v>
+      </c>
+      <c r="L88">
+        <v>-7.18</v>
+      </c>
+      <c r="M88">
+        <v>119.6063232</v>
+      </c>
+      <c r="N88">
+        <v>-126.7863232</v>
+      </c>
+      <c r="O88">
+        <v>-31.69658080000001</v>
+      </c>
+      <c r="P88">
+        <v>-95.08974240000002</v>
+      </c>
+      <c r="Q88">
+        <v>-87.90974240000003</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3004915193572739</v>
+      </c>
+      <c r="T88">
+        <v>3.86760357880668</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.01500756776043091</v>
+      </c>
+      <c r="W88">
+        <v>0.2423838071811909</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.06003027104172354</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2525188868858425</v>
+      </c>
+      <c r="C89">
+        <v>-287.3047000042694</v>
+      </c>
+      <c r="D89">
+        <v>62.78329999573076</v>
+      </c>
+      <c r="E89">
+        <v>160.5880000000001</v>
+      </c>
+      <c r="F89">
+        <v>506.6880000000001</v>
+      </c>
+      <c r="G89">
+        <v>156.6</v>
+      </c>
+      <c r="H89">
+        <v>236.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>7.18</v>
+      </c>
+      <c r="L89">
+        <v>-7.18</v>
+      </c>
+      <c r="M89">
+        <v>120.9970944</v>
+      </c>
+      <c r="N89">
+        <v>-128.1770944</v>
+      </c>
+      <c r="O89">
+        <v>-32.04427360000001</v>
+      </c>
+      <c r="P89">
+        <v>-96.13282080000003</v>
+      </c>
+      <c r="Q89">
+        <v>-88.95282080000004</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3206216362309104</v>
+      </c>
+      <c r="T89">
+        <v>4.165111546407194</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.01483506698157538</v>
+      </c>
+      <c r="W89">
+        <v>0.2423426139952002</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.05934026792630154</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2545188868858425</v>
+      </c>
+      <c r="C90">
+        <v>-293.7107844095996</v>
+      </c>
+      <c r="D90">
+        <v>62.20121559040048</v>
+      </c>
+      <c r="E90">
+        <v>166.412</v>
+      </c>
+      <c r="F90">
+        <v>512.5120000000001</v>
+      </c>
+      <c r="G90">
+        <v>156.6</v>
+      </c>
+      <c r="H90">
+        <v>236.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>7.18</v>
+      </c>
+      <c r="L90">
+        <v>-7.18</v>
+      </c>
+      <c r="M90">
+        <v>122.3878656</v>
+      </c>
+      <c r="N90">
+        <v>-129.5678656</v>
+      </c>
+      <c r="O90">
+        <v>-32.39196640000001</v>
+      </c>
+      <c r="P90">
+        <v>-97.17589920000003</v>
+      </c>
+      <c r="Q90">
+        <v>-89.99589920000003</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3441067725834863</v>
+      </c>
+      <c r="T90">
+        <v>4.51220417527446</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.01466648667496657</v>
+      </c>
+      <c r="W90">
+        <v>0.242302357017982</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.05866594669986624</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2565188868858425</v>
+      </c>
+      <c r="C91">
+        <v>-300.106174576802</v>
+      </c>
+      <c r="D91">
+        <v>61.62982542319816</v>
+      </c>
+      <c r="E91">
+        <v>172.2360000000001</v>
+      </c>
+      <c r="F91">
+        <v>518.3360000000001</v>
+      </c>
+      <c r="G91">
+        <v>156.6</v>
+      </c>
+      <c r="H91">
+        <v>236.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>7.18</v>
+      </c>
+      <c r="L91">
+        <v>-7.18</v>
+      </c>
+      <c r="M91">
+        <v>123.7786368</v>
+      </c>
+      <c r="N91">
+        <v>-130.9586368</v>
+      </c>
+      <c r="O91">
+        <v>-32.73965920000001</v>
+      </c>
+      <c r="P91">
+        <v>-98.21897760000002</v>
+      </c>
+      <c r="Q91">
+        <v>-91.03897760000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3718619337274396</v>
+      </c>
+      <c r="T91">
+        <v>4.922404554844866</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.01450169468985459</v>
+      </c>
+      <c r="W91">
+        <v>0.2422630046919373</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.05800677875941829</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2585188868858425</v>
+      </c>
+      <c r="C92">
+        <v>-306.4911625400736</v>
+      </c>
+      <c r="D92">
+        <v>61.06883745992653</v>
+      </c>
+      <c r="E92">
+        <v>178.0600000000001</v>
+      </c>
+      <c r="F92">
+        <v>524.1600000000001</v>
+      </c>
+      <c r="G92">
+        <v>156.6</v>
+      </c>
+      <c r="H92">
+        <v>236.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>7.18</v>
+      </c>
+      <c r="L92">
+        <v>-7.18</v>
+      </c>
+      <c r="M92">
+        <v>125.169408</v>
+      </c>
+      <c r="N92">
+        <v>-132.349408</v>
+      </c>
+      <c r="O92">
+        <v>-33.08735200000001</v>
+      </c>
+      <c r="P92">
+        <v>-99.26205600000003</v>
+      </c>
+      <c r="Q92">
+        <v>-92.08205600000002</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4051681271001836</v>
+      </c>
+      <c r="T92">
+        <v>5.414645010329354</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.0143405647488562</v>
+      </c>
+      <c r="W92">
+        <v>0.2422245268620269</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.0573622589954248</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2605188868858425</v>
+      </c>
+      <c r="C93">
+        <v>-312.8660297965141</v>
+      </c>
+      <c r="D93">
+        <v>60.51797020348602</v>
+      </c>
+      <c r="E93">
+        <v>183.8840000000001</v>
+      </c>
+      <c r="F93">
+        <v>529.9840000000002</v>
+      </c>
+      <c r="G93">
+        <v>156.6</v>
+      </c>
+      <c r="H93">
+        <v>236.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>7.18</v>
+      </c>
+      <c r="L93">
+        <v>-7.18</v>
+      </c>
+      <c r="M93">
+        <v>126.5601792</v>
+      </c>
+      <c r="N93">
+        <v>-133.7401792</v>
+      </c>
+      <c r="O93">
+        <v>-33.43504480000001</v>
+      </c>
+      <c r="P93">
+        <v>-100.3051344</v>
+      </c>
+      <c r="Q93">
+        <v>-93.12513440000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4458756967779818</v>
+      </c>
+      <c r="T93">
+        <v>6.016272233699282</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.0141829761252424</v>
+      </c>
+      <c r="W93">
+        <v>0.2421868946987079</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.05673190450096954</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2625188868858425</v>
+      </c>
+      <c r="C94">
+        <v>-319.2310477771226</v>
+      </c>
+      <c r="D94">
+        <v>59.97695222287746</v>
+      </c>
+      <c r="E94">
+        <v>189.7080000000001</v>
+      </c>
+      <c r="F94">
+        <v>535.8080000000001</v>
+      </c>
+      <c r="G94">
+        <v>156.6</v>
+      </c>
+      <c r="H94">
+        <v>236.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>7.18</v>
+      </c>
+      <c r="L94">
+        <v>-7.18</v>
+      </c>
+      <c r="M94">
+        <v>127.9509504</v>
+      </c>
+      <c r="N94">
+        <v>-135.1309504</v>
+      </c>
+      <c r="O94">
+        <v>-33.78273760000001</v>
+      </c>
+      <c r="P94">
+        <v>-101.3482128</v>
+      </c>
+      <c r="Q94">
+        <v>-94.16821280000002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.4967601588752296</v>
+      </c>
+      <c r="T94">
+        <v>6.768306262911693</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.01402881334127237</v>
+      </c>
+      <c r="W94">
+        <v>0.2421500806258958</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.05611525336508949</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2645188868858425</v>
+      </c>
+      <c r="C95">
+        <v>-325.5864782927552</v>
+      </c>
+      <c r="D95">
+        <v>59.44552170724486</v>
+      </c>
+      <c r="E95">
+        <v>195.532</v>
+      </c>
+      <c r="F95">
+        <v>541.6320000000001</v>
+      </c>
+      <c r="G95">
+        <v>156.6</v>
+      </c>
+      <c r="H95">
+        <v>236.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>7.18</v>
+      </c>
+      <c r="L95">
+        <v>-7.18</v>
+      </c>
+      <c r="M95">
+        <v>129.3417216</v>
+      </c>
+      <c r="N95">
+        <v>-136.5217216</v>
+      </c>
+      <c r="O95">
+        <v>-34.13043040000001</v>
+      </c>
+      <c r="P95">
+        <v>-102.3912912</v>
+      </c>
+      <c r="Q95">
+        <v>-95.21129120000003</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5621830387145483</v>
+      </c>
+      <c r="T95">
+        <v>7.735207157613366</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.01387796588598987</v>
+      </c>
+      <c r="W95">
+        <v>0.2421140582535744</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.05551186354395954</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2665188868858426</v>
+      </c>
+      <c r="C96">
+        <v>-331.9325739565817</v>
+      </c>
+      <c r="D96">
+        <v>58.92342604341839</v>
+      </c>
+      <c r="E96">
+        <v>201.3560000000001</v>
+      </c>
+      <c r="F96">
+        <v>547.4560000000001</v>
+      </c>
+      <c r="G96">
+        <v>156.6</v>
+      </c>
+      <c r="H96">
+        <v>236.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>7.18</v>
+      </c>
+      <c r="L96">
+        <v>-7.18</v>
+      </c>
+      <c r="M96">
+        <v>130.7324928</v>
+      </c>
+      <c r="N96">
+        <v>-137.9124928000001</v>
+      </c>
+      <c r="O96">
+        <v>-34.47812320000001</v>
+      </c>
+      <c r="P96">
+        <v>-103.4343696</v>
+      </c>
+      <c r="Q96">
+        <v>-96.25436960000005</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.6494135451669731</v>
+      </c>
+      <c r="T96">
+        <v>9.024408350548928</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.01373032795103253</v>
+      </c>
+      <c r="W96">
+        <v>0.2420788023147066</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.05492131180413029</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2685188868858426</v>
+      </c>
+      <c r="C97">
+        <v>-338.2695785844746</v>
+      </c>
+      <c r="D97">
+        <v>58.41042141552551</v>
+      </c>
+      <c r="E97">
+        <v>207.1800000000001</v>
+      </c>
+      <c r="F97">
+        <v>553.2800000000001</v>
+      </c>
+      <c r="G97">
+        <v>156.6</v>
+      </c>
+      <c r="H97">
+        <v>236.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>7.18</v>
+      </c>
+      <c r="L97">
+        <v>-7.18</v>
+      </c>
+      <c r="M97">
+        <v>132.123264</v>
+      </c>
+      <c r="N97">
+        <v>-139.303264</v>
+      </c>
+      <c r="O97">
+        <v>-34.82581600000001</v>
+      </c>
+      <c r="P97">
+        <v>-104.477448</v>
+      </c>
+      <c r="Q97">
+        <v>-97.29744800000003</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.7715362542003681</v>
+      </c>
+      <c r="T97">
+        <v>10.82929002065872</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.01358579818312693</v>
+      </c>
+      <c r="W97">
+        <v>0.2420442886061307</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.05434319273250776</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2705188868858425</v>
+      </c>
+      <c r="C98">
+        <v>-344.5977275746628</v>
+      </c>
+      <c r="D98">
+        <v>57.90627242533723</v>
+      </c>
+      <c r="E98">
+        <v>213.004</v>
+      </c>
+      <c r="F98">
+        <v>559.104</v>
+      </c>
+      <c r="G98">
+        <v>156.6</v>
+      </c>
+      <c r="H98">
+        <v>236.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>7.18</v>
+      </c>
+      <c r="L98">
+        <v>-7.18</v>
+      </c>
+      <c r="M98">
+        <v>133.5140352</v>
+      </c>
+      <c r="N98">
+        <v>-140.6940352</v>
+      </c>
+      <c r="O98">
+        <v>-35.17350880000001</v>
+      </c>
+      <c r="P98">
+        <v>-105.5205264</v>
+      </c>
+      <c r="Q98">
+        <v>-98.34052640000002</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.9547203177504582</v>
+      </c>
+      <c r="T98">
+        <v>13.53661252582337</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.01344427945205269</v>
+      </c>
+      <c r="W98">
+        <v>0.2420104939331502</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.05377711780821071</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2725188868858425</v>
+      </c>
+      <c r="C99">
+        <v>-350.9172482678931</v>
+      </c>
+      <c r="D99">
+        <v>57.41075173210701</v>
+      </c>
+      <c r="E99">
+        <v>218.8280000000001</v>
+      </c>
+      <c r="F99">
+        <v>564.9280000000001</v>
+      </c>
+      <c r="G99">
+        <v>156.6</v>
+      </c>
+      <c r="H99">
+        <v>236.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>7.18</v>
+      </c>
+      <c r="L99">
+        <v>-7.18</v>
+      </c>
+      <c r="M99">
+        <v>134.9048064</v>
+      </c>
+      <c r="N99">
+        <v>-142.0848064</v>
+      </c>
+      <c r="O99">
+        <v>-35.52120160000001</v>
+      </c>
+      <c r="P99">
+        <v>-106.5636048</v>
+      </c>
+      <c r="Q99">
+        <v>-99.38360480000003</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.260027090333944</v>
+      </c>
+      <c r="T99">
+        <v>18.04881670109783</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.01330567863295936</v>
+      </c>
+      <c r="W99">
+        <v>0.2419773960575507</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.05322271453183758</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2745188868858425</v>
+      </c>
+      <c r="C100">
+        <v>-357.2283602892553</v>
+      </c>
+      <c r="D100">
+        <v>56.92363971074477</v>
+      </c>
+      <c r="E100">
+        <v>224.652</v>
+      </c>
+      <c r="F100">
+        <v>570.7520000000001</v>
+      </c>
+      <c r="G100">
+        <v>156.6</v>
+      </c>
+      <c r="H100">
+        <v>236.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>7.18</v>
+      </c>
+      <c r="L100">
+        <v>-7.18</v>
+      </c>
+      <c r="M100">
+        <v>136.2955776</v>
+      </c>
+      <c r="N100">
+        <v>-143.4755776</v>
+      </c>
+      <c r="O100">
+        <v>-35.86889440000001</v>
+      </c>
+      <c r="P100">
+        <v>-107.6066832</v>
+      </c>
+      <c r="Q100">
+        <v>-100.4266832</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.870640635500916</v>
+      </c>
+      <c r="T100">
+        <v>27.07322505164674</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.0131699064020108</v>
+      </c>
+      <c r="W100">
+        <v>0.2419449736488002</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.05267962560804329</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2765188868858425</v>
+      </c>
+      <c r="C101">
+        <v>-363.5312758727536</v>
+      </c>
+      <c r="D101">
+        <v>56.44472412724652</v>
+      </c>
+      <c r="E101">
+        <v>230.4760000000001</v>
+      </c>
+      <c r="F101">
+        <v>576.5760000000001</v>
+      </c>
+      <c r="G101">
+        <v>156.6</v>
+      </c>
+      <c r="H101">
+        <v>236.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>7.18</v>
+      </c>
+      <c r="L101">
+        <v>-7.18</v>
+      </c>
+      <c r="M101">
+        <v>137.6863488</v>
+      </c>
+      <c r="N101">
+        <v>-144.8663488000001</v>
+      </c>
+      <c r="O101">
+        <v>-36.21658720000001</v>
+      </c>
+      <c r="P101">
+        <v>-108.6497616</v>
+      </c>
+      <c r="Q101">
+        <v>-101.4697616</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.702481271001833</v>
+      </c>
+      <c r="T101">
+        <v>54.14645010329348</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.01303687704441473</v>
+      </c>
+      <c r="W101">
+        <v>0.2419132062382063</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.05214750817765901</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
